--- a/research/traditional_assets/database/data/jordan/jordan_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_business_consumer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1328755558829831</v>
+        <v>0.1326458047712171</v>
       </c>
       <c r="C2">
-        <v>7.116955012302885</v>
+        <v>7.052553809436535</v>
       </c>
       <c r="D2">
-        <v>5.016955012302885</v>
+        <v>5.023353809436535</v>
       </c>
       <c r="E2">
-        <v>-1.41</v>
+        <v>-1.3392</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
       <c r="G2">
         <v>2.1</v>
@@ -1451,28 +1451,28 @@
         <v>1.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00356124</v>
       </c>
       <c r="N2">
-        <v>1.5</v>
+        <v>1.49643876</v>
       </c>
       <c r="O2">
-        <v>0.3</v>
+        <v>0.299287752</v>
       </c>
       <c r="P2">
-        <v>1.2</v>
+        <v>1.197151008</v>
       </c>
       <c r="Q2">
-        <v>1.28</v>
+        <v>1.277151008</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1328755558829831</v>
+        <v>0.1335791967386032</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9612181828672363</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>421.2016039357078</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1326458047712171</v>
+        <v>0.1324160536594511</v>
       </c>
       <c r="C3">
-        <v>7.052553809436535</v>
+        <v>6.98816894990733</v>
       </c>
       <c r="D3">
-        <v>5.023353809436535</v>
+        <v>5.029768949907329</v>
       </c>
       <c r="E3">
-        <v>-1.3392</v>
+        <v>-1.2684</v>
       </c>
       <c r="F3">
-        <v>0.0708</v>
+        <v>0.1416</v>
       </c>
       <c r="G3">
         <v>2.1</v>
@@ -1533,28 +1533,28 @@
         <v>1.5</v>
       </c>
       <c r="M3">
-        <v>0.00356124</v>
+        <v>0.00712248</v>
       </c>
       <c r="N3">
-        <v>1.49643876</v>
+        <v>1.49287752</v>
       </c>
       <c r="O3">
-        <v>0.299287752</v>
+        <v>0.298575504</v>
       </c>
       <c r="P3">
-        <v>1.197151008</v>
+        <v>1.194302016</v>
       </c>
       <c r="Q3">
-        <v>1.277151008</v>
+        <v>1.274302016</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1335791967386032</v>
+        <v>0.1342971976116848</v>
       </c>
       <c r="T3">
-        <v>0.9612181828672363</v>
+        <v>0.9690805867187534</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>421.2016039357078</v>
+        <v>210.6008019678539</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1324160536594511</v>
+        <v>0.1321863025476852</v>
       </c>
       <c r="C4">
-        <v>6.98816894990733</v>
+        <v>6.92380049640976</v>
       </c>
       <c r="D4">
-        <v>5.029768949907329</v>
+        <v>5.03620049640976</v>
       </c>
       <c r="E4">
-        <v>-1.2684</v>
+        <v>-1.1976</v>
       </c>
       <c r="F4">
-        <v>0.1416</v>
+        <v>0.2124</v>
       </c>
       <c r="G4">
         <v>2.1</v>
@@ -1615,28 +1615,28 @@
         <v>1.5</v>
       </c>
       <c r="M4">
-        <v>0.00712248</v>
+        <v>0.01068372</v>
       </c>
       <c r="N4">
-        <v>1.49287752</v>
+        <v>1.48931628</v>
       </c>
       <c r="O4">
-        <v>0.298575504</v>
+        <v>0.297863256</v>
       </c>
       <c r="P4">
-        <v>1.194302016</v>
+        <v>1.191453024</v>
       </c>
       <c r="Q4">
-        <v>1.274302016</v>
+        <v>1.271453024</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1342971976116848</v>
+        <v>0.1350300026264796</v>
       </c>
       <c r="T4">
-        <v>0.9690805867187534</v>
+        <v>0.9771051019898894</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>210.6008019678539</v>
+        <v>140.400534645236</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1321863025476852</v>
+        <v>0.1319565514359192</v>
       </c>
       <c r="C5">
-        <v>6.92380049640976</v>
+        <v>6.859448511959397</v>
       </c>
       <c r="D5">
-        <v>5.03620049640976</v>
+        <v>5.042648511959397</v>
       </c>
       <c r="E5">
-        <v>-1.1976</v>
+        <v>-1.1268</v>
       </c>
       <c r="F5">
-        <v>0.2124</v>
+        <v>0.2832</v>
       </c>
       <c r="G5">
         <v>2.1</v>
@@ -1697,28 +1697,28 @@
         <v>1.5</v>
       </c>
       <c r="M5">
-        <v>0.01068372</v>
+        <v>0.01424496</v>
       </c>
       <c r="N5">
-        <v>1.48931628</v>
+        <v>1.48575504</v>
       </c>
       <c r="O5">
-        <v>0.297863256</v>
+        <v>0.297151008</v>
       </c>
       <c r="P5">
-        <v>1.191453024</v>
+        <v>1.188604032</v>
       </c>
       <c r="Q5">
-        <v>1.271453024</v>
+        <v>1.268604032</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1350300026264796</v>
+        <v>0.1357780744124159</v>
       </c>
       <c r="T5">
-        <v>0.9771051019898894</v>
+        <v>0.9852967946625077</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>140.400534645236</v>
+        <v>105.3004009839269</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1319565514359192</v>
+        <v>0.1317268003241532</v>
       </c>
       <c r="C6">
-        <v>6.859448511959397</v>
+        <v>6.795113059894947</v>
       </c>
       <c r="D6">
-        <v>5.042648511959397</v>
+        <v>5.049113059894948</v>
       </c>
       <c r="E6">
-        <v>-1.1268</v>
+        <v>-1.056</v>
       </c>
       <c r="F6">
-        <v>0.2832</v>
+        <v>0.354</v>
       </c>
       <c r="G6">
         <v>2.1</v>
@@ -1779,28 +1779,28 @@
         <v>1.5</v>
       </c>
       <c r="M6">
-        <v>0.01424496</v>
+        <v>0.0178062</v>
       </c>
       <c r="N6">
-        <v>1.48575504</v>
+        <v>1.4821938</v>
       </c>
       <c r="O6">
-        <v>0.297151008</v>
+        <v>0.29643876</v>
       </c>
       <c r="P6">
-        <v>1.188604032</v>
+        <v>1.18575504</v>
       </c>
       <c r="Q6">
-        <v>1.268604032</v>
+        <v>1.26575504</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1357780744124159</v>
+        <v>0.1365418950780561</v>
       </c>
       <c r="T6">
-        <v>0.9852967946625077</v>
+        <v>0.9936609440229702</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>105.3004009839269</v>
+        <v>84.24032078714154</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1317268003241532</v>
+        <v>0.1314970492123873</v>
       </c>
       <c r="C7">
-        <v>6.795113059894947</v>
+        <v>6.730794203880326</v>
       </c>
       <c r="D7">
-        <v>5.049113059894948</v>
+        <v>5.055594203880327</v>
       </c>
       <c r="E7">
-        <v>-1.056</v>
+        <v>-0.9851999999999999</v>
       </c>
       <c r="F7">
-        <v>0.354</v>
+        <v>0.4248</v>
       </c>
       <c r="G7">
         <v>2.1</v>
@@ -1861,28 +1861,28 @@
         <v>1.5</v>
       </c>
       <c r="M7">
-        <v>0.0178062</v>
+        <v>0.02136744</v>
       </c>
       <c r="N7">
-        <v>1.4821938</v>
+        <v>1.47863256</v>
       </c>
       <c r="O7">
-        <v>0.29643876</v>
+        <v>0.2957265120000001</v>
       </c>
       <c r="P7">
-        <v>1.18575504</v>
+        <v>1.182906048</v>
       </c>
       <c r="Q7">
-        <v>1.26575504</v>
+        <v>1.262906048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1365418950780561</v>
+        <v>0.1373219672472205</v>
       </c>
       <c r="T7">
-        <v>0.9936609440229702</v>
+        <v>1.002203054008124</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>84.24032078714154</v>
+        <v>70.20026732261798</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1314970492123873</v>
+        <v>0.1312672981006213</v>
       </c>
       <c r="C8">
-        <v>6.730794203880326</v>
+        <v>6.666492007906756</v>
       </c>
       <c r="D8">
-        <v>5.055594203880327</v>
+        <v>5.062092007906756</v>
       </c>
       <c r="E8">
-        <v>-0.9851999999999999</v>
+        <v>-0.9144</v>
       </c>
       <c r="F8">
-        <v>0.4248</v>
+        <v>0.4955999999999999</v>
       </c>
       <c r="G8">
         <v>2.1</v>
@@ -1943,28 +1943,28 @@
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>0.02136744</v>
+        <v>0.02492867999999999</v>
       </c>
       <c r="N8">
-        <v>1.47863256</v>
+        <v>1.47507132</v>
       </c>
       <c r="O8">
-        <v>0.2957265120000001</v>
+        <v>0.295014264</v>
       </c>
       <c r="P8">
-        <v>1.182906048</v>
+        <v>1.180057056</v>
       </c>
       <c r="Q8">
-        <v>1.262906048</v>
+        <v>1.260057056</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1373219672472205</v>
+        <v>0.1381188151619584</v>
       </c>
       <c r="T8">
-        <v>1.002203054008124</v>
+        <v>1.010928865283281</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>70.20026732261798</v>
+        <v>60.17165770510113</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1312672981006213</v>
+        <v>0.1310375469888554</v>
       </c>
       <c r="C9">
-        <v>6.666492007906758</v>
+        <v>6.602206536294863</v>
       </c>
       <c r="D9">
-        <v>5.062092007906757</v>
+        <v>5.068606536294863</v>
       </c>
       <c r="E9">
-        <v>-0.9143999999999999</v>
+        <v>-0.8435999999999999</v>
       </c>
       <c r="F9">
-        <v>0.4956</v>
+        <v>0.5664</v>
       </c>
       <c r="G9">
         <v>2.1</v>
@@ -2025,28 +2025,28 @@
         <v>1.5</v>
       </c>
       <c r="M9">
-        <v>0.02492868</v>
+        <v>0.02848992</v>
       </c>
       <c r="N9">
-        <v>1.47507132</v>
+        <v>1.47151008</v>
       </c>
       <c r="O9">
-        <v>0.295014264</v>
+        <v>0.294302016</v>
       </c>
       <c r="P9">
-        <v>1.180057056</v>
+        <v>1.177208064</v>
       </c>
       <c r="Q9">
-        <v>1.260057056</v>
+        <v>1.257208064</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1381188151619584</v>
+        <v>0.1389329858574515</v>
       </c>
       <c r="T9">
-        <v>1.010928865283281</v>
+        <v>1.019844368107897</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>60.17165770510111</v>
+        <v>52.65020049196348</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1310375469888554</v>
+        <v>0.1308077958770894</v>
       </c>
       <c r="C10">
-        <v>6.602206536294863</v>
+        <v>6.537937853696802</v>
       </c>
       <c r="D10">
-        <v>5.068606536294863</v>
+        <v>5.075137853696802</v>
       </c>
       <c r="E10">
-        <v>-0.8435999999999999</v>
+        <v>-0.7727999999999999</v>
       </c>
       <c r="F10">
-        <v>0.5664</v>
+        <v>0.6372</v>
       </c>
       <c r="G10">
         <v>2.1</v>
@@ -2107,28 +2107,28 @@
         <v>1.5</v>
       </c>
       <c r="M10">
-        <v>0.02848992</v>
+        <v>0.03205116</v>
       </c>
       <c r="N10">
-        <v>1.47151008</v>
+        <v>1.46794884</v>
       </c>
       <c r="O10">
-        <v>0.294302016</v>
+        <v>0.293589768</v>
       </c>
       <c r="P10">
-        <v>1.177208064</v>
+        <v>1.174359072</v>
       </c>
       <c r="Q10">
-        <v>1.257208064</v>
+        <v>1.254359072</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1389329858574515</v>
+        <v>0.1397650504143839</v>
       </c>
       <c r="T10">
-        <v>1.019844368107897</v>
+        <v>1.028955816049538</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>52.65020049196348</v>
+        <v>46.80017821507865</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1308077958770894</v>
+        <v>0.1305780447653234</v>
       </c>
       <c r="C11">
-        <v>6.537937853696802</v>
+        <v>6.473686025098401</v>
       </c>
       <c r="D11">
-        <v>5.075137853696802</v>
+        <v>5.0816860250984</v>
       </c>
       <c r="E11">
-        <v>-0.7727999999999999</v>
+        <v>-0.702</v>
       </c>
       <c r="F11">
-        <v>0.6372</v>
+        <v>0.708</v>
       </c>
       <c r="G11">
         <v>2.1</v>
@@ -2189,28 +2189,28 @@
         <v>1.5</v>
       </c>
       <c r="M11">
-        <v>0.03205116</v>
+        <v>0.0356124</v>
       </c>
       <c r="N11">
-        <v>1.46794884</v>
+        <v>1.4643876</v>
       </c>
       <c r="O11">
-        <v>0.293589768</v>
+        <v>0.29287752</v>
       </c>
       <c r="P11">
-        <v>1.174359072</v>
+        <v>1.17151008</v>
       </c>
       <c r="Q11">
-        <v>1.254359072</v>
+        <v>1.25151008</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1397650504143839</v>
+        <v>0.1406156052948038</v>
       </c>
       <c r="T11">
-        <v>1.028955816049538</v>
+        <v>1.038269740612105</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>46.80017821507865</v>
+        <v>42.12016039357079</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1305780447653234</v>
+        <v>0.1303482936535575</v>
       </c>
       <c r="C12">
-        <v>6.473686025098401</v>
+        <v>6.409451115821305</v>
       </c>
       <c r="D12">
-        <v>5.0816860250984</v>
+        <v>5.088251115821305</v>
       </c>
       <c r="E12">
-        <v>-0.7019999999999998</v>
+        <v>-0.6311999999999999</v>
       </c>
       <c r="F12">
-        <v>0.7080000000000001</v>
+        <v>0.7788</v>
       </c>
       <c r="G12">
         <v>2.1</v>
@@ -2271,28 +2271,28 @@
         <v>1.5</v>
       </c>
       <c r="M12">
-        <v>0.0356124</v>
+        <v>0.03917364</v>
       </c>
       <c r="N12">
-        <v>1.4643876</v>
+        <v>1.46082636</v>
       </c>
       <c r="O12">
-        <v>0.29287752</v>
+        <v>0.292165272</v>
       </c>
       <c r="P12">
-        <v>1.17151008</v>
+        <v>1.168661088</v>
       </c>
       <c r="Q12">
-        <v>1.25151008</v>
+        <v>1.248661088</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1406156052948038</v>
+        <v>0.1414852737680421</v>
       </c>
       <c r="T12">
-        <v>1.038269740612105</v>
+        <v>1.047792966850235</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.12016039357078</v>
+        <v>38.29105490324616</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1303482936535575</v>
+        <v>0.1301185425417915</v>
       </c>
       <c r="C13">
-        <v>6.409451115821305</v>
+        <v>6.345233191525163</v>
       </c>
       <c r="D13">
-        <v>5.088251115821305</v>
+        <v>5.094833191525162</v>
       </c>
       <c r="E13">
-        <v>-0.6311999999999999</v>
+        <v>-0.5603999999999999</v>
       </c>
       <c r="F13">
-        <v>0.7788</v>
+        <v>0.8496</v>
       </c>
       <c r="G13">
         <v>2.1</v>
@@ -2353,28 +2353,28 @@
         <v>1.5</v>
       </c>
       <c r="M13">
-        <v>0.03917364</v>
+        <v>0.04273488</v>
       </c>
       <c r="N13">
-        <v>1.46082636</v>
+        <v>1.45726512</v>
       </c>
       <c r="O13">
-        <v>0.292165272</v>
+        <v>0.291453024</v>
       </c>
       <c r="P13">
-        <v>1.168661088</v>
+        <v>1.165812096</v>
       </c>
       <c r="Q13">
-        <v>1.248661088</v>
+        <v>1.245812096</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1414852737680421</v>
+        <v>0.142374707433854</v>
       </c>
       <c r="T13">
-        <v>1.047792966850235</v>
+        <v>1.057532630048322</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.29105490324616</v>
+        <v>35.10013366130899</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1301185425417915</v>
+        <v>0.1298887914300255</v>
       </c>
       <c r="C14">
-        <v>6.345233191525163</v>
+        <v>6.281032318209802</v>
       </c>
       <c r="D14">
-        <v>5.094833191525162</v>
+        <v>5.101432318209802</v>
       </c>
       <c r="E14">
-        <v>-0.5603999999999999</v>
+        <v>-0.4895999999999999</v>
       </c>
       <c r="F14">
-        <v>0.8496</v>
+        <v>0.9204</v>
       </c>
       <c r="G14">
         <v>2.1</v>
@@ -2435,28 +2435,28 @@
         <v>1.5</v>
       </c>
       <c r="M14">
-        <v>0.04273488</v>
+        <v>0.04629612</v>
       </c>
       <c r="N14">
-        <v>1.45726512</v>
+        <v>1.45370388</v>
       </c>
       <c r="O14">
-        <v>0.291453024</v>
+        <v>0.290740776</v>
       </c>
       <c r="P14">
-        <v>1.165812096</v>
+        <v>1.162963104</v>
       </c>
       <c r="Q14">
-        <v>1.245812096</v>
+        <v>1.242963104</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.142374707433854</v>
+        <v>0.1432845878506041</v>
       </c>
       <c r="T14">
-        <v>1.057532630048322</v>
+        <v>1.067496193549814</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.10013366130899</v>
+        <v>32.40012337966984</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1298887914300255</v>
+        <v>0.1296590403182596</v>
       </c>
       <c r="C15">
-        <v>6.281032318209802</v>
+        <v>6.216848562217444</v>
       </c>
       <c r="D15">
-        <v>5.101432318209802</v>
+        <v>5.108048562217443</v>
       </c>
       <c r="E15">
-        <v>-0.4895999999999999</v>
+        <v>-0.4187999999999998</v>
       </c>
       <c r="F15">
-        <v>0.9204</v>
+        <v>0.9912000000000001</v>
       </c>
       <c r="G15">
         <v>2.1</v>
@@ -2517,28 +2517,28 @@
         <v>1.5</v>
       </c>
       <c r="M15">
-        <v>0.04629612</v>
+        <v>0.04985736</v>
       </c>
       <c r="N15">
-        <v>1.45370388</v>
+        <v>1.45014264</v>
       </c>
       <c r="O15">
-        <v>0.290740776</v>
+        <v>0.290028528</v>
       </c>
       <c r="P15">
-        <v>1.162963104</v>
+        <v>1.160114112</v>
       </c>
       <c r="Q15">
-        <v>1.242963104</v>
+        <v>1.240114112</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1432845878506041</v>
+        <v>0.144215628277046</v>
       </c>
       <c r="T15">
-        <v>1.067496193549814</v>
+        <v>1.07769146783041</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.40012337966984</v>
+        <v>30.08582885255055</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1296590403182596</v>
+        <v>0.1294292892064936</v>
       </c>
       <c r="C16">
-        <v>6.216848562217444</v>
+        <v>6.15268199023492</v>
       </c>
       <c r="D16">
-        <v>5.108048562217443</v>
+        <v>5.114681990234921</v>
       </c>
       <c r="E16">
-        <v>-0.4187999999999998</v>
+        <v>-0.3479999999999996</v>
       </c>
       <c r="F16">
-        <v>0.9912000000000001</v>
+        <v>1.062</v>
       </c>
       <c r="G16">
         <v>2.1</v>
@@ -2599,28 +2599,28 @@
         <v>1.5</v>
       </c>
       <c r="M16">
-        <v>0.04985736</v>
+        <v>0.05341860000000001</v>
       </c>
       <c r="N16">
-        <v>1.45014264</v>
+        <v>1.4465814</v>
       </c>
       <c r="O16">
-        <v>0.290028528</v>
+        <v>0.28931628</v>
       </c>
       <c r="P16">
-        <v>1.160114112</v>
+        <v>1.15726512</v>
       </c>
       <c r="Q16">
-        <v>1.240114112</v>
+        <v>1.23726512</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.144215628277046</v>
+        <v>0.1451685755370513</v>
       </c>
       <c r="T16">
-        <v>1.07769146783041</v>
+        <v>1.088126630917608</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.08582885255055</v>
+        <v>28.08010692904718</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1294292892064936</v>
+        <v>0.1291995380947276</v>
       </c>
       <c r="C17">
-        <v>6.15268199023492</v>
+        <v>6.088532669295928</v>
       </c>
       <c r="D17">
-        <v>5.114681990234921</v>
+        <v>5.121332669295927</v>
       </c>
       <c r="E17">
-        <v>-0.3479999999999999</v>
+        <v>-0.2771999999999999</v>
       </c>
       <c r="F17">
-        <v>1.062</v>
+        <v>1.1328</v>
       </c>
       <c r="G17">
         <v>2.1</v>
@@ -2681,28 +2681,28 @@
         <v>1.5</v>
       </c>
       <c r="M17">
-        <v>0.0534186</v>
+        <v>0.05697984</v>
       </c>
       <c r="N17">
-        <v>1.4465814</v>
+        <v>1.44302016</v>
       </c>
       <c r="O17">
-        <v>0.28931628</v>
+        <v>0.288604032</v>
       </c>
       <c r="P17">
-        <v>1.15726512</v>
+        <v>1.154416128</v>
       </c>
       <c r="Q17">
-        <v>1.23726512</v>
+        <v>1.234416128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1451685755370513</v>
+        <v>0.1461442120175329</v>
       </c>
       <c r="T17">
-        <v>1.088126630917608</v>
+        <v>1.098810250268787</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.08010692904719</v>
+        <v>26.32510024598174</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1291995380947276</v>
+        <v>0.1289697869829617</v>
       </c>
       <c r="C18">
-        <v>6.088532669295928</v>
+        <v>6.02440066678326</v>
       </c>
       <c r="D18">
-        <v>5.121332669295927</v>
+        <v>5.12800066678326</v>
       </c>
       <c r="E18">
-        <v>-0.2771999999999999</v>
+        <v>-0.2063999999999999</v>
       </c>
       <c r="F18">
-        <v>1.1328</v>
+        <v>1.2036</v>
       </c>
       <c r="G18">
         <v>2.1</v>
@@ -2763,28 +2763,28 @@
         <v>1.5</v>
       </c>
       <c r="M18">
-        <v>0.05697984</v>
+        <v>0.06054108</v>
       </c>
       <c r="N18">
-        <v>1.44302016</v>
+        <v>1.43945892</v>
       </c>
       <c r="O18">
-        <v>0.288604032</v>
+        <v>0.287891784</v>
       </c>
       <c r="P18">
-        <v>1.154416128</v>
+        <v>1.151567136</v>
       </c>
       <c r="Q18">
-        <v>1.234416128</v>
+        <v>1.231567136</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1461442120175329</v>
+        <v>0.1471433578107972</v>
       </c>
       <c r="T18">
-        <v>1.098810250268787</v>
+        <v>1.109751306230838</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.32510024598174</v>
+        <v>24.77656493739458</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1289697869829617</v>
+        <v>0.1287400358711957</v>
       </c>
       <c r="C19">
-        <v>6.02440066678326</v>
+        <v>5.960286050431112</v>
       </c>
       <c r="D19">
-        <v>5.12800066678326</v>
+        <v>5.134686050431111</v>
       </c>
       <c r="E19">
-        <v>-0.2063999999999999</v>
+        <v>-0.1355999999999997</v>
       </c>
       <c r="F19">
-        <v>1.2036</v>
+        <v>1.2744</v>
       </c>
       <c r="G19">
         <v>2.1</v>
@@ -2845,28 +2845,28 @@
         <v>1.5</v>
       </c>
       <c r="M19">
-        <v>0.06054108</v>
+        <v>0.06410232</v>
       </c>
       <c r="N19">
-        <v>1.43945892</v>
+        <v>1.43589768</v>
       </c>
       <c r="O19">
-        <v>0.287891784</v>
+        <v>0.287179536</v>
       </c>
       <c r="P19">
-        <v>1.151567136</v>
+        <v>1.148718144</v>
       </c>
       <c r="Q19">
-        <v>1.231567136</v>
+        <v>1.228718144</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1471433578107972</v>
+        <v>0.1481668730136533</v>
       </c>
       <c r="T19">
-        <v>1.109751306230838</v>
+        <v>1.120959217216354</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.77656493739458</v>
+        <v>23.40008910753932</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1287400358711957</v>
+        <v>0.1285102847594297</v>
       </c>
       <c r="C20">
-        <v>5.960286050431112</v>
+        <v>5.896188888327353</v>
       </c>
       <c r="D20">
-        <v>5.134686050431111</v>
+        <v>5.141388888327353</v>
       </c>
       <c r="E20">
-        <v>-0.1355999999999999</v>
+        <v>-0.06479999999999997</v>
       </c>
       <c r="F20">
-        <v>1.2744</v>
+        <v>1.3452</v>
       </c>
       <c r="G20">
         <v>2.1</v>
@@ -2927,28 +2927,28 @@
         <v>1.5</v>
       </c>
       <c r="M20">
-        <v>0.06410231999999999</v>
+        <v>0.06766356</v>
       </c>
       <c r="N20">
-        <v>1.43589768</v>
+        <v>1.43233644</v>
       </c>
       <c r="O20">
-        <v>0.287179536</v>
+        <v>0.286467288</v>
       </c>
       <c r="P20">
-        <v>1.148718144</v>
+        <v>1.145869152</v>
       </c>
       <c r="Q20">
-        <v>1.228718144</v>
+        <v>1.225869152</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1481668730136533</v>
+        <v>0.1492156601968268</v>
       </c>
       <c r="T20">
-        <v>1.120959217216354</v>
+        <v>1.132443866744722</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.40008910753933</v>
+        <v>22.16850547030041</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1285102847594297</v>
+        <v>0.1282805336476638</v>
       </c>
       <c r="C21">
-        <v>5.896188888327353</v>
+        <v>5.832109248915851</v>
       </c>
       <c r="D21">
-        <v>5.141388888327353</v>
+        <v>5.148109248915851</v>
       </c>
       <c r="E21">
-        <v>-0.06479999999999997</v>
+        <v>0.006000000000000227</v>
       </c>
       <c r="F21">
-        <v>1.3452</v>
+        <v>1.416</v>
       </c>
       <c r="G21">
         <v>2.1</v>
@@ -3009,28 +3009,28 @@
         <v>1.5</v>
       </c>
       <c r="M21">
-        <v>0.06766356</v>
+        <v>0.0712248</v>
       </c>
       <c r="N21">
-        <v>1.43233644</v>
+        <v>1.4287752</v>
       </c>
       <c r="O21">
-        <v>0.286467288</v>
+        <v>0.28575504</v>
       </c>
       <c r="P21">
-        <v>1.145869152</v>
+        <v>1.14302016</v>
       </c>
       <c r="Q21">
-        <v>1.225869152</v>
+        <v>1.22302016</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1492156601968268</v>
+        <v>0.1502906670595797</v>
       </c>
       <c r="T21">
-        <v>1.132443866744722</v>
+        <v>1.144215632511299</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.16850547030041</v>
+        <v>21.06008019678539</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1282805336476638</v>
+        <v>0.1280507825358978</v>
       </c>
       <c r="C22">
-        <v>5.832109248915851</v>
+        <v>5.768047200998792</v>
       </c>
       <c r="D22">
-        <v>5.148109248915851</v>
+        <v>5.154847200998793</v>
       </c>
       <c r="E22">
-        <v>0.006000000000000227</v>
+        <v>0.0768000000000002</v>
       </c>
       <c r="F22">
-        <v>1.416</v>
+        <v>1.4868</v>
       </c>
       <c r="G22">
         <v>2.1</v>
@@ -3091,28 +3091,28 @@
         <v>1.5</v>
       </c>
       <c r="M22">
-        <v>0.0712248</v>
+        <v>0.07478604</v>
       </c>
       <c r="N22">
-        <v>1.4287752</v>
+        <v>1.42521396</v>
       </c>
       <c r="O22">
-        <v>0.28575504</v>
+        <v>0.285042792</v>
       </c>
       <c r="P22">
-        <v>1.14302016</v>
+        <v>1.140171168</v>
       </c>
       <c r="Q22">
-        <v>1.22302016</v>
+        <v>1.220171168</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1502906670595797</v>
+        <v>0.1513928892859466</v>
       </c>
       <c r="T22">
-        <v>1.144215632511299</v>
+        <v>1.156285417664372</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.06008019678539</v>
+        <v>20.05721923503371</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1280507825358978</v>
+        <v>0.1278210314241318</v>
       </c>
       <c r="C23">
-        <v>5.768047200998793</v>
+        <v>5.704002813739039</v>
       </c>
       <c r="D23">
-        <v>5.154847200998793</v>
+        <v>5.161602813739039</v>
       </c>
       <c r="E23">
-        <v>0.07679999999999998</v>
+        <v>0.1476000000000002</v>
       </c>
       <c r="F23">
-        <v>1.4868</v>
+        <v>1.5576</v>
       </c>
       <c r="G23">
         <v>2.1</v>
@@ -3173,28 +3173,28 @@
         <v>1.5</v>
       </c>
       <c r="M23">
-        <v>0.07478604</v>
+        <v>0.07834728000000001</v>
       </c>
       <c r="N23">
-        <v>1.42521396</v>
+        <v>1.42165272</v>
       </c>
       <c r="O23">
-        <v>0.285042792</v>
+        <v>0.284330544</v>
       </c>
       <c r="P23">
-        <v>1.140171168</v>
+        <v>1.137322176</v>
       </c>
       <c r="Q23">
-        <v>1.220171168</v>
+        <v>1.217322176</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1513928892859466</v>
+        <v>0.1525233736206818</v>
       </c>
       <c r="T23">
-        <v>1.156285417664372</v>
+        <v>1.168664684488036</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.05721923503371</v>
+        <v>19.14552745162308</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1278210314241318</v>
+        <v>0.1275912803123659</v>
       </c>
       <c r="C24">
-        <v>5.704002813739039</v>
+        <v>5.639976156662487</v>
       </c>
       <c r="D24">
-        <v>5.161602813739039</v>
+        <v>5.168376156662487</v>
       </c>
       <c r="E24">
-        <v>0.1476000000000002</v>
+        <v>0.2184000000000001</v>
       </c>
       <c r="F24">
-        <v>1.5576</v>
+        <v>1.6284</v>
       </c>
       <c r="G24">
         <v>2.1</v>
@@ -3255,28 +3255,28 @@
         <v>1.5</v>
       </c>
       <c r="M24">
-        <v>0.07834728000000001</v>
+        <v>0.08190852</v>
       </c>
       <c r="N24">
-        <v>1.42165272</v>
+        <v>1.41809148</v>
       </c>
       <c r="O24">
-        <v>0.284330544</v>
+        <v>0.283618296</v>
       </c>
       <c r="P24">
-        <v>1.137322176</v>
+        <v>1.134473184</v>
       </c>
       <c r="Q24">
-        <v>1.217322176</v>
+        <v>1.214473184</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1525233736206818</v>
+        <v>0.1536832211848907</v>
       </c>
       <c r="T24">
-        <v>1.168664684488036</v>
+        <v>1.181365490709718</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.14552745162308</v>
+        <v>18.31311321459599</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1275912803123659</v>
+        <v>0.1273615292005999</v>
       </c>
       <c r="C25">
-        <v>5.639976156662487</v>
+        <v>5.575967299660451</v>
       </c>
       <c r="D25">
-        <v>5.168376156662487</v>
+        <v>5.175167299660451</v>
       </c>
       <c r="E25">
-        <v>0.2184000000000001</v>
+        <v>0.2892000000000001</v>
       </c>
       <c r="F25">
-        <v>1.6284</v>
+        <v>1.6992</v>
       </c>
       <c r="G25">
         <v>2.1</v>
@@ -3337,28 +3337,28 @@
         <v>1.5</v>
       </c>
       <c r="M25">
-        <v>0.08190852</v>
+        <v>0.08546975999999999</v>
       </c>
       <c r="N25">
-        <v>1.41809148</v>
+        <v>1.41453024</v>
       </c>
       <c r="O25">
-        <v>0.283618296</v>
+        <v>0.282906048</v>
       </c>
       <c r="P25">
-        <v>1.134473184</v>
+        <v>1.131624192</v>
       </c>
       <c r="Q25">
-        <v>1.214473184</v>
+        <v>1.211624192</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1536832211848907</v>
+        <v>0.1548735910534209</v>
       </c>
       <c r="T25">
-        <v>1.181365490709718</v>
+        <v>1.194400528674076</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.31311321459599</v>
+        <v>17.55006683065449</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1273615292005999</v>
+        <v>0.1271317780888339</v>
       </c>
       <c r="C26">
-        <v>5.575967299660451</v>
+        <v>5.511976312992084</v>
       </c>
       <c r="D26">
-        <v>5.175167299660451</v>
+        <v>5.181976312992084</v>
       </c>
       <c r="E26">
-        <v>0.2892000000000001</v>
+        <v>0.3600000000000001</v>
       </c>
       <c r="F26">
-        <v>1.6992</v>
+        <v>1.77</v>
       </c>
       <c r="G26">
         <v>2.1</v>
@@ -3419,28 +3419,28 @@
         <v>1.5</v>
       </c>
       <c r="M26">
-        <v>0.08546975999999999</v>
+        <v>0.089031</v>
       </c>
       <c r="N26">
-        <v>1.41453024</v>
+        <v>1.410969</v>
       </c>
       <c r="O26">
-        <v>0.282906048</v>
+        <v>0.2821938</v>
       </c>
       <c r="P26">
-        <v>1.131624192</v>
+        <v>1.1287752</v>
       </c>
       <c r="Q26">
-        <v>1.211624192</v>
+        <v>1.2087752</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1548735910534209</v>
+        <v>0.1560957041184452</v>
       </c>
       <c r="T26">
-        <v>1.194400528674075</v>
+        <v>1.207783167650816</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.55006683065449</v>
+        <v>16.84806415742831</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1271317780888339</v>
+        <v>0.126902026977068</v>
       </c>
       <c r="C27">
-        <v>5.511976312992084</v>
+        <v>5.448003267286776</v>
       </c>
       <c r="D27">
-        <v>5.181976312992084</v>
+        <v>5.188803267286775</v>
       </c>
       <c r="E27">
-        <v>0.3600000000000001</v>
+        <v>0.4308000000000001</v>
       </c>
       <c r="F27">
-        <v>1.77</v>
+        <v>1.8408</v>
       </c>
       <c r="G27">
         <v>2.1</v>
@@ -3501,28 +3501,28 @@
         <v>1.5</v>
       </c>
       <c r="M27">
-        <v>0.089031</v>
+        <v>0.09259223999999999</v>
       </c>
       <c r="N27">
-        <v>1.410969</v>
+        <v>1.40740776</v>
       </c>
       <c r="O27">
-        <v>0.2821938</v>
+        <v>0.281481552</v>
       </c>
       <c r="P27">
-        <v>1.1287752</v>
+        <v>1.125926208</v>
       </c>
       <c r="Q27">
-        <v>1.2087752</v>
+        <v>1.205926208</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1560957041184452</v>
+        <v>0.1573508472663081</v>
       </c>
       <c r="T27">
-        <v>1.207783167650816</v>
+        <v>1.221527499572874</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.84806415742831</v>
+        <v>16.20006168983491</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.126902026977068</v>
+        <v>0.126672275865302</v>
       </c>
       <c r="C28">
-        <v>5.448003267286776</v>
+        <v>5.384048233546617</v>
       </c>
       <c r="D28">
-        <v>5.188803267286775</v>
+        <v>5.195648233546617</v>
       </c>
       <c r="E28">
-        <v>0.4308000000000001</v>
+        <v>0.5016000000000003</v>
       </c>
       <c r="F28">
-        <v>1.8408</v>
+        <v>1.9116</v>
       </c>
       <c r="G28">
         <v>2.1</v>
@@ -3583,28 +3583,28 @@
         <v>1.5</v>
       </c>
       <c r="M28">
-        <v>0.09259223999999999</v>
+        <v>0.09615348</v>
       </c>
       <c r="N28">
-        <v>1.40740776</v>
+        <v>1.40384652</v>
       </c>
       <c r="O28">
-        <v>0.281481552</v>
+        <v>0.2807693040000001</v>
       </c>
       <c r="P28">
-        <v>1.125926208</v>
+        <v>1.123077216</v>
       </c>
       <c r="Q28">
-        <v>1.205926208</v>
+        <v>1.203077216</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1573508472663081</v>
+        <v>0.158640377897674</v>
       </c>
       <c r="T28">
-        <v>1.221527499572874</v>
+        <v>1.235648388533892</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.20006168983491</v>
+        <v>15.60005940502622</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.126672275865302</v>
+        <v>0.126442524753536</v>
       </c>
       <c r="C29">
-        <v>5.384048233546617</v>
+        <v>5.320111283148846</v>
       </c>
       <c r="D29">
-        <v>5.195648233546617</v>
+        <v>5.202511283148845</v>
       </c>
       <c r="E29">
-        <v>0.5016000000000003</v>
+        <v>0.5724000000000002</v>
       </c>
       <c r="F29">
-        <v>1.9116</v>
+        <v>1.9824</v>
       </c>
       <c r="G29">
         <v>2.1</v>
@@ -3665,28 +3665,28 @@
         <v>1.5</v>
       </c>
       <c r="M29">
-        <v>0.09615348</v>
+        <v>0.09971472000000001</v>
       </c>
       <c r="N29">
-        <v>1.40384652</v>
+        <v>1.40028528</v>
       </c>
       <c r="O29">
-        <v>0.2807693040000001</v>
+        <v>0.280057056</v>
       </c>
       <c r="P29">
-        <v>1.123077216</v>
+        <v>1.120228224</v>
       </c>
       <c r="Q29">
-        <v>1.203077216</v>
+        <v>1.200228224</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.158640377897674</v>
+        <v>0.1599657288243556</v>
       </c>
       <c r="T29">
-        <v>1.235648388533892</v>
+        <v>1.250161524410494</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.60005940502622</v>
+        <v>15.04291442627528</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.126442524753536</v>
+        <v>0.1262127736417701</v>
       </c>
       <c r="C30">
-        <v>5.320111283148846</v>
+        <v>5.256192487848335</v>
       </c>
       <c r="D30">
-        <v>5.202511283148845</v>
+        <v>5.209392487848335</v>
       </c>
       <c r="E30">
-        <v>0.5724000000000002</v>
+        <v>0.6432000000000004</v>
       </c>
       <c r="F30">
-        <v>1.9824</v>
+        <v>2.0532</v>
       </c>
       <c r="G30">
         <v>2.1</v>
@@ -3747,28 +3747,28 @@
         <v>1.5</v>
       </c>
       <c r="M30">
-        <v>0.09971472000000001</v>
+        <v>0.10327596</v>
       </c>
       <c r="N30">
-        <v>1.40028528</v>
+        <v>1.39672404</v>
       </c>
       <c r="O30">
-        <v>0.280057056</v>
+        <v>0.279344808</v>
       </c>
       <c r="P30">
-        <v>1.120228224</v>
+        <v>1.117379232</v>
       </c>
       <c r="Q30">
-        <v>1.200228224</v>
+        <v>1.197379232</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1599657288243556</v>
+        <v>0.1613284135799578</v>
       </c>
       <c r="T30">
-        <v>1.250161524410494</v>
+        <v>1.265083481016014</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.04291442627528</v>
+        <v>14.52419323916234</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1262127736417701</v>
+        <v>0.1259830225300041</v>
       </c>
       <c r="C31">
-        <v>5.256192487848335</v>
+        <v>5.192291919780095</v>
       </c>
       <c r="D31">
-        <v>5.209392487848335</v>
+        <v>5.216291919780096</v>
       </c>
       <c r="E31">
-        <v>0.6432</v>
+        <v>0.7140000000000002</v>
       </c>
       <c r="F31">
-        <v>2.0532</v>
+        <v>2.124</v>
       </c>
       <c r="G31">
         <v>2.1</v>
@@ -3829,28 +3829,28 @@
         <v>1.5</v>
       </c>
       <c r="M31">
-        <v>0.10327596</v>
+        <v>0.1068372</v>
       </c>
       <c r="N31">
-        <v>1.39672404</v>
+        <v>1.3931628</v>
       </c>
       <c r="O31">
-        <v>0.279344808</v>
+        <v>0.27863256</v>
       </c>
       <c r="P31">
-        <v>1.117379232</v>
+        <v>1.11453024</v>
       </c>
       <c r="Q31">
-        <v>1.197379232</v>
+        <v>1.19453024</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1613284135799578</v>
+        <v>0.1627300321857202</v>
       </c>
       <c r="T31">
-        <v>1.265083481016014</v>
+        <v>1.280431779238835</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.52419323916234</v>
+        <v>14.04005346452359</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1259830225300041</v>
+        <v>0.1257532714182381</v>
       </c>
       <c r="C32">
-        <v>5.192291919780095</v>
+        <v>5.128409651461792</v>
       </c>
       <c r="D32">
-        <v>5.216291919780096</v>
+        <v>5.223209651461792</v>
       </c>
       <c r="E32">
-        <v>0.7140000000000002</v>
+        <v>0.7847999999999999</v>
       </c>
       <c r="F32">
-        <v>2.124</v>
+        <v>2.1948</v>
       </c>
       <c r="G32">
         <v>2.1</v>
@@ -3911,28 +3911,28 @@
         <v>1.5</v>
       </c>
       <c r="M32">
-        <v>0.1068372</v>
+        <v>0.11039844</v>
       </c>
       <c r="N32">
-        <v>1.3931628</v>
+        <v>1.38960156</v>
       </c>
       <c r="O32">
-        <v>0.27863256</v>
+        <v>0.277920312</v>
       </c>
       <c r="P32">
-        <v>1.11453024</v>
+        <v>1.111681248</v>
       </c>
       <c r="Q32">
-        <v>1.19453024</v>
+        <v>1.191681248</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1627300321857202</v>
+        <v>0.1641722774177364</v>
       </c>
       <c r="T32">
-        <v>1.280431779238835</v>
+        <v>1.296224955671013</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.04005346452359</v>
+        <v>13.58714851405509</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1257532714182381</v>
+        <v>0.1255235203064722</v>
       </c>
       <c r="C33">
-        <v>5.128409651461792</v>
+        <v>5.064545755796284</v>
       </c>
       <c r="D33">
-        <v>5.223209651461792</v>
+        <v>5.230145755796284</v>
       </c>
       <c r="E33">
-        <v>0.7847999999999999</v>
+        <v>0.8556000000000001</v>
       </c>
       <c r="F33">
-        <v>2.1948</v>
+        <v>2.2656</v>
       </c>
       <c r="G33">
         <v>2.1</v>
@@ -3993,28 +3993,28 @@
         <v>1.5</v>
       </c>
       <c r="M33">
-        <v>0.11039844</v>
+        <v>0.11395968</v>
       </c>
       <c r="N33">
-        <v>1.38960156</v>
+        <v>1.38604032</v>
       </c>
       <c r="O33">
-        <v>0.277920312</v>
+        <v>0.277208064</v>
       </c>
       <c r="P33">
-        <v>1.111681248</v>
+        <v>1.108832256</v>
       </c>
       <c r="Q33">
-        <v>1.191681248</v>
+        <v>1.188832256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1641722774177364</v>
+        <v>0.165656941627165</v>
       </c>
       <c r="T33">
-        <v>1.296224955671013</v>
+        <v>1.312482637292373</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.58714851405509</v>
+        <v>13.16255012299087</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1255235203064722</v>
+        <v>0.1256897691947062</v>
       </c>
       <c r="C34">
-        <v>5.064545755796284</v>
+        <v>4.988724920613712</v>
       </c>
       <c r="D34">
-        <v>5.230145755796284</v>
+        <v>5.225124920613712</v>
       </c>
       <c r="E34">
-        <v>0.8556000000000001</v>
+        <v>0.9264000000000003</v>
       </c>
       <c r="F34">
-        <v>2.2656</v>
+        <v>2.3364</v>
       </c>
       <c r="G34">
         <v>2.1</v>
@@ -4075,45 +4075,45 @@
         <v>1.5</v>
       </c>
       <c r="M34">
-        <v>0.11395968</v>
+        <v>0.12102552</v>
       </c>
       <c r="N34">
-        <v>1.38604032</v>
+        <v>1.37897448</v>
       </c>
       <c r="O34">
-        <v>0.277208064</v>
+        <v>0.275794896</v>
       </c>
       <c r="P34">
-        <v>1.108832256</v>
+        <v>1.103179584</v>
       </c>
       <c r="Q34">
-        <v>1.188832256</v>
+        <v>1.183179584</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.165656941627165</v>
+        <v>0.1671859241712033</v>
       </c>
       <c r="T34">
-        <v>1.312482637292373</v>
+        <v>1.329225622842728</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>13.16255012299087</v>
+        <v>12.39408019069036</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1256897691947062</v>
+        <v>0.1254720180829402</v>
       </c>
       <c r="C35">
-        <v>4.988724920613712</v>
+        <v>4.924503117920562</v>
       </c>
       <c r="D35">
-        <v>5.225124920613712</v>
+        <v>5.231703117920562</v>
       </c>
       <c r="E35">
-        <v>0.9264000000000003</v>
+        <v>0.9972000000000001</v>
       </c>
       <c r="F35">
-        <v>2.3364</v>
+        <v>2.4072</v>
       </c>
       <c r="G35">
         <v>2.1</v>
@@ -4157,28 +4157,28 @@
         <v>1.5</v>
       </c>
       <c r="M35">
-        <v>0.12102552</v>
+        <v>0.12469296</v>
       </c>
       <c r="N35">
-        <v>1.37897448</v>
+        <v>1.37530704</v>
       </c>
       <c r="O35">
-        <v>0.275794896</v>
+        <v>0.275061408</v>
       </c>
       <c r="P35">
-        <v>1.103179584</v>
+        <v>1.100245632</v>
       </c>
       <c r="Q35">
-        <v>1.183179584</v>
+        <v>1.180245632</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1671859241712033</v>
+        <v>0.1687612395196064</v>
       </c>
       <c r="T35">
-        <v>1.329225622842728</v>
+        <v>1.346475971591579</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.39408019069036</v>
+        <v>12.02954842037594</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1254720180829402</v>
+        <v>0.1252542669711743</v>
       </c>
       <c r="C36">
-        <v>4.924503117920562</v>
+        <v>4.860297899415349</v>
       </c>
       <c r="D36">
-        <v>5.231703117920562</v>
+        <v>5.238297899415348</v>
       </c>
       <c r="E36">
-        <v>0.9972000000000001</v>
+        <v>1.068</v>
       </c>
       <c r="F36">
-        <v>2.4072</v>
+        <v>2.478</v>
       </c>
       <c r="G36">
         <v>2.1</v>
@@ -4239,28 +4239,28 @@
         <v>1.5</v>
       </c>
       <c r="M36">
-        <v>0.12469296</v>
+        <v>0.1283604</v>
       </c>
       <c r="N36">
-        <v>1.37530704</v>
+        <v>1.3716396</v>
       </c>
       <c r="O36">
-        <v>0.275061408</v>
+        <v>0.27432792</v>
       </c>
       <c r="P36">
-        <v>1.100245632</v>
+        <v>1.09731168</v>
       </c>
       <c r="Q36">
-        <v>1.180245632</v>
+        <v>1.17731168</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1687612395196064</v>
+        <v>0.1703850261094989</v>
       </c>
       <c r="T36">
-        <v>1.346475971591579</v>
+        <v>1.364257100301934</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.02954842037594</v>
+        <v>11.68584703693662</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1252542669711743</v>
+        <v>0.1250365158594083</v>
       </c>
       <c r="C37">
-        <v>4.860297899415349</v>
+        <v>4.79610932789242</v>
       </c>
       <c r="D37">
-        <v>5.238297899415348</v>
+        <v>5.24490932789242</v>
       </c>
       <c r="E37">
-        <v>1.068</v>
+        <v>1.1388</v>
       </c>
       <c r="F37">
-        <v>2.478</v>
+        <v>2.5488</v>
       </c>
       <c r="G37">
         <v>2.1</v>
@@ -4321,28 +4321,28 @@
         <v>1.5</v>
       </c>
       <c r="M37">
-        <v>0.1283604</v>
+        <v>0.13202784</v>
       </c>
       <c r="N37">
-        <v>1.3716396</v>
+        <v>1.36797216</v>
       </c>
       <c r="O37">
-        <v>0.27432792</v>
+        <v>0.273594432</v>
       </c>
       <c r="P37">
-        <v>1.09731168</v>
+        <v>1.094377728</v>
       </c>
       <c r="Q37">
-        <v>1.17731168</v>
+        <v>1.174377728</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1703850261094989</v>
+        <v>0.1720595560303255</v>
       </c>
       <c r="T37">
-        <v>1.364257100301934</v>
+        <v>1.382593889284487</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.68584703693662</v>
+        <v>11.3612401747995</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1250365158594083</v>
+        <v>0.1248187647476423</v>
       </c>
       <c r="C38">
-        <v>4.79610932789242</v>
+        <v>4.731937466463553</v>
       </c>
       <c r="D38">
-        <v>5.24490932789242</v>
+        <v>5.251537466463552</v>
       </c>
       <c r="E38">
-        <v>1.1388</v>
+        <v>1.2096</v>
       </c>
       <c r="F38">
-        <v>2.5488</v>
+        <v>2.6196</v>
       </c>
       <c r="G38">
         <v>2.1</v>
@@ -4403,28 +4403,28 @@
         <v>1.5</v>
       </c>
       <c r="M38">
-        <v>0.13202784</v>
+        <v>0.13569528</v>
       </c>
       <c r="N38">
-        <v>1.36797216</v>
+        <v>1.36430472</v>
       </c>
       <c r="O38">
-        <v>0.273594432</v>
+        <v>0.272860944</v>
       </c>
       <c r="P38">
-        <v>1.094377728</v>
+        <v>1.091443776</v>
       </c>
       <c r="Q38">
-        <v>1.174377728</v>
+        <v>1.171443776</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1720595560303255</v>
+        <v>0.1737872456311783</v>
       </c>
       <c r="T38">
-        <v>1.382593889284486</v>
+        <v>1.4015127985522</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.3612401747995</v>
+        <v>11.05417962953465</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1248187647476423</v>
+        <v>0.1246010136358764</v>
       </c>
       <c r="C39">
-        <v>4.731937466463553</v>
+        <v>4.667782378559943</v>
       </c>
       <c r="D39">
-        <v>5.251537466463552</v>
+        <v>5.258182378559943</v>
       </c>
       <c r="E39">
-        <v>1.2096</v>
+        <v>1.2804</v>
       </c>
       <c r="F39">
-        <v>2.6196</v>
+        <v>2.6904</v>
       </c>
       <c r="G39">
         <v>2.1</v>
@@ -4485,28 +4485,28 @@
         <v>1.5</v>
       </c>
       <c r="M39">
-        <v>0.13569528</v>
+        <v>0.13936272</v>
       </c>
       <c r="N39">
-        <v>1.36430472</v>
+        <v>1.36063728</v>
       </c>
       <c r="O39">
-        <v>0.272860944</v>
+        <v>0.272127456</v>
       </c>
       <c r="P39">
-        <v>1.091443776</v>
+        <v>1.088509824</v>
       </c>
       <c r="Q39">
-        <v>1.171443776</v>
+        <v>1.168509824</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1737872456311783</v>
+        <v>0.1755706671546393</v>
       </c>
       <c r="T39">
-        <v>1.4015127985522</v>
+        <v>1.421041995215646</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.05417962953465</v>
+        <v>10.76328016559952</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1246010136358764</v>
+        <v>0.1243832625241104</v>
       </c>
       <c r="C40">
-        <v>4.667782378559943</v>
+        <v>4.603644127934242</v>
       </c>
       <c r="D40">
-        <v>5.258182378559943</v>
+        <v>5.264844127934242</v>
       </c>
       <c r="E40">
-        <v>1.2804</v>
+        <v>1.3512</v>
       </c>
       <c r="F40">
-        <v>2.6904</v>
+        <v>2.7612</v>
       </c>
       <c r="G40">
         <v>2.1</v>
@@ -4567,28 +4567,28 @@
         <v>1.5</v>
       </c>
       <c r="M40">
-        <v>0.13936272</v>
+        <v>0.14303016</v>
       </c>
       <c r="N40">
-        <v>1.36063728</v>
+        <v>1.35696984</v>
       </c>
       <c r="O40">
-        <v>0.272127456</v>
+        <v>0.271393968</v>
       </c>
       <c r="P40">
-        <v>1.088509824</v>
+        <v>1.085575872</v>
       </c>
       <c r="Q40">
-        <v>1.168509824</v>
+        <v>1.165575872</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1755706671546393</v>
+        <v>0.1774125615149351</v>
       </c>
       <c r="T40">
-        <v>1.421041995215646</v>
+        <v>1.441211493409041</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.76328016559952</v>
+        <v>10.48729862289184</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1243832625241104</v>
+        <v>0.1241655114123445</v>
       </c>
       <c r="C41">
-        <v>4.603644127934242</v>
+        <v>4.539522778662588</v>
       </c>
       <c r="D41">
-        <v>5.264844127934242</v>
+        <v>5.271522778662589</v>
       </c>
       <c r="E41">
-        <v>1.3512</v>
+        <v>1.422</v>
       </c>
       <c r="F41">
-        <v>2.7612</v>
+        <v>2.832</v>
       </c>
       <c r="G41">
         <v>2.1</v>
@@ -4649,28 +4649,28 @@
         <v>1.5</v>
       </c>
       <c r="M41">
-        <v>0.14303016</v>
+        <v>0.1466976</v>
       </c>
       <c r="N41">
-        <v>1.35696984</v>
+        <v>1.3533024</v>
       </c>
       <c r="O41">
-        <v>0.271393968</v>
+        <v>0.27066048</v>
       </c>
       <c r="P41">
-        <v>1.085575872</v>
+        <v>1.08264192</v>
       </c>
       <c r="Q41">
-        <v>1.165575872</v>
+        <v>1.16264192</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1774125615149351</v>
+        <v>0.1793158523539074</v>
       </c>
       <c r="T41">
-        <v>1.441211493409041</v>
+        <v>1.462053308208882</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.48729862289184</v>
+        <v>10.22511615731955</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1241655114123445</v>
+        <v>0.1239477603005785</v>
       </c>
       <c r="C42">
-        <v>4.539522778662588</v>
+        <v>4.475418395146673</v>
       </c>
       <c r="D42">
-        <v>5.271522778662589</v>
+        <v>5.278218395146673</v>
       </c>
       <c r="E42">
-        <v>1.422</v>
+        <v>1.4928</v>
       </c>
       <c r="F42">
-        <v>2.832</v>
+        <v>2.9028</v>
       </c>
       <c r="G42">
         <v>2.1</v>
@@ -4731,28 +4731,28 @@
         <v>1.5</v>
       </c>
       <c r="M42">
-        <v>0.1466976</v>
+        <v>0.15036504</v>
       </c>
       <c r="N42">
-        <v>1.3533024</v>
+        <v>1.34963496</v>
       </c>
       <c r="O42">
-        <v>0.27066048</v>
+        <v>0.269926992</v>
       </c>
       <c r="P42">
-        <v>1.08264192</v>
+        <v>1.079707968</v>
       </c>
       <c r="Q42">
-        <v>1.16264192</v>
+        <v>1.159707968</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1793158523539074</v>
+        <v>0.1812836615264042</v>
       </c>
       <c r="T42">
-        <v>1.462053308208882</v>
+        <v>1.483601625205329</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.22511615731955</v>
+        <v>9.975723080311752</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1239477603005785</v>
+        <v>0.1243012091888125</v>
       </c>
       <c r="C43">
-        <v>4.475418395146673</v>
+        <v>4.393758800273901</v>
       </c>
       <c r="D43">
-        <v>5.278218395146673</v>
+        <v>5.267358800273901</v>
       </c>
       <c r="E43">
-        <v>1.4928</v>
+        <v>1.5636</v>
       </c>
       <c r="F43">
-        <v>2.9028</v>
+        <v>2.9736</v>
       </c>
       <c r="G43">
         <v>2.1</v>
@@ -4813,45 +4813,45 @@
         <v>1.5</v>
       </c>
       <c r="M43">
-        <v>0.15036504</v>
+        <v>0.1590876</v>
       </c>
       <c r="N43">
-        <v>1.34963496</v>
+        <v>1.3409124</v>
       </c>
       <c r="O43">
-        <v>0.269926992</v>
+        <v>0.26818248</v>
       </c>
       <c r="P43">
-        <v>1.079707968</v>
+        <v>1.07272992</v>
       </c>
       <c r="Q43">
-        <v>1.159707968</v>
+        <v>1.15272992</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1812836615264042</v>
+        <v>0.1833193261876078</v>
       </c>
       <c r="T43">
-        <v>1.483601625205329</v>
+        <v>1.505892987615446</v>
       </c>
       <c r="U43">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>9.975723080311752</v>
+        <v>9.428767546936403</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1243012091888125</v>
+        <v>0.1240970580770466</v>
       </c>
       <c r="C44">
-        <v>4.393758800273902</v>
+        <v>4.329225814908973</v>
       </c>
       <c r="D44">
-        <v>5.267358800273901</v>
+        <v>5.273625814908972</v>
       </c>
       <c r="E44">
-        <v>1.5636</v>
+        <v>1.6344</v>
       </c>
       <c r="F44">
-        <v>2.9736</v>
+        <v>3.0444</v>
       </c>
       <c r="G44">
         <v>2.1</v>
@@ -4895,28 +4895,28 @@
         <v>1.5</v>
       </c>
       <c r="M44">
-        <v>0.1590876</v>
+        <v>0.1628754</v>
       </c>
       <c r="N44">
-        <v>1.3409124</v>
+        <v>1.3371246</v>
       </c>
       <c r="O44">
-        <v>0.2681824800000001</v>
+        <v>0.26742492</v>
       </c>
       <c r="P44">
-        <v>1.07272992</v>
+        <v>1.06969968</v>
       </c>
       <c r="Q44">
-        <v>1.15272992</v>
+        <v>1.14969968</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1833193261876078</v>
+        <v>0.185426417679029</v>
       </c>
       <c r="T44">
-        <v>1.505892987615445</v>
+        <v>1.528966503092584</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.428767546936406</v>
+        <v>9.209493883054163</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1240970580770466</v>
+        <v>0.1238929069652806</v>
       </c>
       <c r="C45">
-        <v>4.329225814908973</v>
+        <v>4.264707760084713</v>
       </c>
       <c r="D45">
-        <v>5.273625814908972</v>
+        <v>5.279907760084713</v>
       </c>
       <c r="E45">
-        <v>1.6344</v>
+        <v>1.7052</v>
       </c>
       <c r="F45">
-        <v>3.0444</v>
+        <v>3.1152</v>
       </c>
       <c r="G45">
         <v>2.1</v>
@@ -4977,28 +4977,28 @@
         <v>1.5</v>
       </c>
       <c r="M45">
-        <v>0.1628754</v>
+        <v>0.1666632</v>
       </c>
       <c r="N45">
-        <v>1.3371246</v>
+        <v>1.3333368</v>
       </c>
       <c r="O45">
-        <v>0.26742492</v>
+        <v>0.26666736</v>
       </c>
       <c r="P45">
-        <v>1.06969968</v>
+        <v>1.06666944</v>
       </c>
       <c r="Q45">
-        <v>1.14969968</v>
+        <v>1.14666944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.185426417679029</v>
+        <v>0.187608762438001</v>
       </c>
       <c r="T45">
-        <v>1.528966503092584</v>
+        <v>1.552864072693906</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.209493883054163</v>
+        <v>9.000187203893841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1238929069652806</v>
+        <v>0.1236887558535146</v>
       </c>
       <c r="C46">
-        <v>4.264707760084713</v>
+        <v>4.200204689220554</v>
       </c>
       <c r="D46">
-        <v>5.279907760084713</v>
+        <v>5.286204689220554</v>
       </c>
       <c r="E46">
-        <v>1.7052</v>
+        <v>1.776</v>
       </c>
       <c r="F46">
-        <v>3.1152</v>
+        <v>3.186</v>
       </c>
       <c r="G46">
         <v>2.1</v>
@@ -5059,28 +5059,28 @@
         <v>1.5</v>
       </c>
       <c r="M46">
-        <v>0.1666632</v>
+        <v>0.170451</v>
       </c>
       <c r="N46">
-        <v>1.3333368</v>
+        <v>1.329549</v>
       </c>
       <c r="O46">
-        <v>0.26666736</v>
+        <v>0.2659098</v>
       </c>
       <c r="P46">
-        <v>1.06666944</v>
+        <v>1.0636392</v>
       </c>
       <c r="Q46">
-        <v>1.14666944</v>
+        <v>1.1436392</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.187608762438001</v>
+        <v>0.1898704651882084</v>
       </c>
       <c r="T46">
-        <v>1.552864072693906</v>
+        <v>1.577630644826185</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.000187203893841</v>
+        <v>8.800183043807312</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1236887558535146</v>
+        <v>0.1234846047417487</v>
       </c>
       <c r="C47">
-        <v>4.200204689220554</v>
+        <v>4.13571665599107</v>
       </c>
       <c r="D47">
-        <v>5.286204689220554</v>
+        <v>5.292516655991069</v>
       </c>
       <c r="E47">
-        <v>1.776</v>
+        <v>1.8468</v>
       </c>
       <c r="F47">
-        <v>3.186</v>
+        <v>3.2568</v>
       </c>
       <c r="G47">
         <v>2.1</v>
@@ -5141,28 +5141,28 @@
         <v>1.5</v>
       </c>
       <c r="M47">
-        <v>0.170451</v>
+        <v>0.1742388</v>
       </c>
       <c r="N47">
-        <v>1.329549</v>
+        <v>1.3257612</v>
       </c>
       <c r="O47">
-        <v>0.2659098</v>
+        <v>0.26515224</v>
       </c>
       <c r="P47">
-        <v>1.0636392</v>
+        <v>1.06060896</v>
       </c>
       <c r="Q47">
-        <v>1.1436392</v>
+        <v>1.14060896</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1898704651882084</v>
+        <v>0.192215934706942</v>
       </c>
       <c r="T47">
-        <v>1.577630644826185</v>
+        <v>1.603314497407808</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.800183043807312</v>
+        <v>8.608874716768021</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1234846047417487</v>
+        <v>0.1232804536299827</v>
       </c>
       <c r="C48">
-        <v>4.13571665599107</v>
+        <v>4.071243714327494</v>
       </c>
       <c r="D48">
-        <v>5.292516655991069</v>
+        <v>5.298843714327494</v>
       </c>
       <c r="E48">
-        <v>1.8468</v>
+        <v>1.9176</v>
       </c>
       <c r="F48">
-        <v>3.2568</v>
+        <v>3.3276</v>
       </c>
       <c r="G48">
         <v>2.1</v>
@@ -5223,28 +5223,28 @@
         <v>1.5</v>
       </c>
       <c r="M48">
-        <v>0.1742388</v>
+        <v>0.1780266</v>
       </c>
       <c r="N48">
-        <v>1.3257612</v>
+        <v>1.3219734</v>
       </c>
       <c r="O48">
-        <v>0.26515224</v>
+        <v>0.26439468</v>
       </c>
       <c r="P48">
-        <v>1.06060896</v>
+        <v>1.05757872</v>
       </c>
       <c r="Q48">
-        <v>1.14060896</v>
+        <v>1.13757872</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.192215934706942</v>
+        <v>0.1946499125094013</v>
       </c>
       <c r="T48">
-        <v>1.603314497407808</v>
+        <v>1.629967551973643</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.608874716768021</v>
+        <v>8.425707169602745</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1232804536299827</v>
+        <v>0.1230763025182167</v>
       </c>
       <c r="C49">
-        <v>4.071243714327494</v>
+        <v>4.00678591841927</v>
       </c>
       <c r="D49">
-        <v>5.298843714327494</v>
+        <v>5.305185918419271</v>
       </c>
       <c r="E49">
-        <v>1.9176</v>
+        <v>1.9884</v>
       </c>
       <c r="F49">
-        <v>3.3276</v>
+        <v>3.3984</v>
       </c>
       <c r="G49">
         <v>2.1</v>
@@ -5305,28 +5305,28 @@
         <v>1.5</v>
       </c>
       <c r="M49">
-        <v>0.1780266</v>
+        <v>0.1818144</v>
       </c>
       <c r="N49">
-        <v>1.3219734</v>
+        <v>1.3181856</v>
       </c>
       <c r="O49">
-        <v>0.26439468</v>
+        <v>0.26363712</v>
       </c>
       <c r="P49">
-        <v>1.05757872</v>
+        <v>1.05454848</v>
       </c>
       <c r="Q49">
-        <v>1.13757872</v>
+        <v>1.13454848</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1946499125094013</v>
+        <v>0.1971775048427244</v>
       </c>
       <c r="T49">
-        <v>1.629967551973643</v>
+        <v>1.65764572402278</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.425707169602745</v>
+        <v>8.250171603569354</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1230763025182167</v>
+        <v>0.1228721514064508</v>
       </c>
       <c r="C50">
-        <v>4.00678591841927</v>
+        <v>3.942343322715588</v>
       </c>
       <c r="D50">
-        <v>5.305185918419271</v>
+        <v>5.311543322715588</v>
       </c>
       <c r="E50">
-        <v>1.9884</v>
+        <v>2.0592</v>
       </c>
       <c r="F50">
-        <v>3.3984</v>
+        <v>3.4692</v>
       </c>
       <c r="G50">
         <v>2.1</v>
@@ -5387,28 +5387,28 @@
         <v>1.5</v>
       </c>
       <c r="M50">
-        <v>0.1818144</v>
+        <v>0.1856022</v>
       </c>
       <c r="N50">
-        <v>1.3181856</v>
+        <v>1.3143978</v>
       </c>
       <c r="O50">
-        <v>0.26363712</v>
+        <v>0.26287956</v>
       </c>
       <c r="P50">
-        <v>1.05454848</v>
+        <v>1.05151824</v>
       </c>
       <c r="Q50">
-        <v>1.13454848</v>
+        <v>1.13151824</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1971775048427244</v>
+        <v>0.1998042184440211</v>
       </c>
       <c r="T50">
-        <v>1.65764572402278</v>
+        <v>1.686409314583647</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.250171603569354</v>
+        <v>8.081800754516919</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1228721514064508</v>
+        <v>0.1226680002946848</v>
       </c>
       <c r="C51">
-        <v>3.942343322715588</v>
+        <v>3.87791598192694</v>
       </c>
       <c r="D51">
-        <v>5.311543322715588</v>
+        <v>5.31791598192694</v>
       </c>
       <c r="E51">
-        <v>2.0592</v>
+        <v>2.13</v>
       </c>
       <c r="F51">
-        <v>3.4692</v>
+        <v>3.54</v>
       </c>
       <c r="G51">
         <v>2.1</v>
@@ -5469,28 +5469,28 @@
         <v>1.5</v>
       </c>
       <c r="M51">
-        <v>0.1856022</v>
+        <v>0.18939</v>
       </c>
       <c r="N51">
-        <v>1.3143978</v>
+        <v>1.31061</v>
       </c>
       <c r="O51">
-        <v>0.26287956</v>
+        <v>0.262122</v>
       </c>
       <c r="P51">
-        <v>1.05151824</v>
+        <v>1.048488</v>
       </c>
       <c r="Q51">
-        <v>1.13151824</v>
+        <v>1.128488</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1998042184440211</v>
+        <v>0.2025360005893695</v>
       </c>
       <c r="T51">
-        <v>1.686409314583647</v>
+        <v>1.716323448766949</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.081800754516919</v>
+        <v>7.92016473942658</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1226680002946848</v>
+        <v>0.1224638491829188</v>
       </c>
       <c r="C52">
-        <v>3.87791598192694</v>
+        <v>3.813503951026701</v>
       </c>
       <c r="D52">
-        <v>5.31791598192694</v>
+        <v>5.324303951026701</v>
       </c>
       <c r="E52">
-        <v>2.13</v>
+        <v>2.2008</v>
       </c>
       <c r="F52">
-        <v>3.54</v>
+        <v>3.6108</v>
       </c>
       <c r="G52">
         <v>2.1</v>
@@ -5551,28 +5551,28 @@
         <v>1.5</v>
       </c>
       <c r="M52">
-        <v>0.18939</v>
+        <v>0.1931778</v>
       </c>
       <c r="N52">
-        <v>1.31061</v>
+        <v>1.3068222</v>
       </c>
       <c r="O52">
-        <v>0.262122</v>
+        <v>0.26136444</v>
       </c>
       <c r="P52">
-        <v>1.048488</v>
+        <v>1.04545776</v>
       </c>
       <c r="Q52">
-        <v>1.128488</v>
+        <v>1.12545776</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2025360005893695</v>
+        <v>0.2053792840467731</v>
       </c>
       <c r="T52">
-        <v>1.716323448766949</v>
+        <v>1.747458568018957</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.92016473942658</v>
+        <v>7.764867391594686</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1224638491829188</v>
+        <v>0.1222596980711528</v>
       </c>
       <c r="C53">
-        <v>3.813503951026701</v>
+        <v>3.749107285252701</v>
       </c>
       <c r="D53">
-        <v>5.324303951026701</v>
+        <v>5.330707285252702</v>
       </c>
       <c r="E53">
-        <v>2.2008</v>
+        <v>2.2716</v>
       </c>
       <c r="F53">
-        <v>3.6108</v>
+        <v>3.6816</v>
       </c>
       <c r="G53">
         <v>2.1</v>
@@ -5633,28 +5633,28 @@
         <v>1.5</v>
       </c>
       <c r="M53">
-        <v>0.1931778</v>
+        <v>0.1969656</v>
       </c>
       <c r="N53">
-        <v>1.3068222</v>
+        <v>1.3030344</v>
       </c>
       <c r="O53">
-        <v>0.26136444</v>
+        <v>0.26060688</v>
       </c>
       <c r="P53">
-        <v>1.04545776</v>
+        <v>1.04242752</v>
       </c>
       <c r="Q53">
-        <v>1.12545776</v>
+        <v>1.12242752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2053792840467731</v>
+        <v>0.2083410376482351</v>
       </c>
       <c r="T53">
-        <v>1.747458568018957</v>
+        <v>1.779890983906465</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.764867391594686</v>
+        <v>7.615543018679404</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1222596980711528</v>
+        <v>0.1223947469593869</v>
       </c>
       <c r="C54">
-        <v>3.749107285252701</v>
+        <v>3.674069664836215</v>
       </c>
       <c r="D54">
-        <v>5.330707285252702</v>
+        <v>5.326469664836215</v>
       </c>
       <c r="E54">
-        <v>2.2716</v>
+        <v>2.3424</v>
       </c>
       <c r="F54">
-        <v>3.6816</v>
+        <v>3.7524</v>
       </c>
       <c r="G54">
         <v>2.1</v>
@@ -5715,45 +5715,45 @@
         <v>1.5</v>
       </c>
       <c r="M54">
-        <v>0.1969656</v>
+        <v>0.20375532</v>
       </c>
       <c r="N54">
-        <v>1.3030344</v>
+        <v>1.29624468</v>
       </c>
       <c r="O54">
-        <v>0.26060688</v>
+        <v>0.259248936</v>
       </c>
       <c r="P54">
-        <v>1.04242752</v>
+        <v>1.036995744</v>
       </c>
       <c r="Q54">
-        <v>1.12242752</v>
+        <v>1.116995744</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2083410376482351</v>
+        <v>0.2114288233178444</v>
       </c>
       <c r="T54">
-        <v>1.779890983906465</v>
+        <v>1.813703502597698</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.615543018679404</v>
+        <v>7.361770971182494</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1223947469593869</v>
+        <v>0.1221969958476209</v>
       </c>
       <c r="C55">
-        <v>3.674069664836215</v>
+        <v>3.609477074708596</v>
       </c>
       <c r="D55">
-        <v>5.326469664836215</v>
+        <v>5.332677074708596</v>
       </c>
       <c r="E55">
-        <v>2.3424</v>
+        <v>2.413200000000001</v>
       </c>
       <c r="F55">
-        <v>3.7524</v>
+        <v>3.8232</v>
       </c>
       <c r="G55">
         <v>2.1</v>
@@ -5797,28 +5797,28 @@
         <v>1.5</v>
       </c>
       <c r="M55">
-        <v>0.20375532</v>
+        <v>0.20759976</v>
       </c>
       <c r="N55">
-        <v>1.29624468</v>
+        <v>1.29240024</v>
       </c>
       <c r="O55">
-        <v>0.259248936</v>
+        <v>0.258480048</v>
       </c>
       <c r="P55">
-        <v>1.036995744</v>
+        <v>1.033920192</v>
       </c>
       <c r="Q55">
-        <v>1.116995744</v>
+        <v>1.113920192</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2114288233178444</v>
+        <v>0.2146508605383063</v>
       </c>
       <c r="T55">
-        <v>1.813703502597698</v>
+        <v>1.848986130797244</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.361770971182494</v>
+        <v>7.22544187912356</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1221969958476209</v>
+        <v>0.121999244735855</v>
       </c>
       <c r="C56">
-        <v>3.609477074708596</v>
+        <v>3.544898969557646</v>
       </c>
       <c r="D56">
-        <v>5.332677074708596</v>
+        <v>5.338898969557647</v>
       </c>
       <c r="E56">
-        <v>2.413200000000001</v>
+        <v>2.484000000000001</v>
       </c>
       <c r="F56">
-        <v>3.8232</v>
+        <v>3.894000000000001</v>
       </c>
       <c r="G56">
         <v>2.1</v>
@@ -5879,28 +5879,28 @@
         <v>1.5</v>
       </c>
       <c r="M56">
-        <v>0.20759976</v>
+        <v>0.2114442</v>
       </c>
       <c r="N56">
-        <v>1.29240024</v>
+        <v>1.2885558</v>
       </c>
       <c r="O56">
-        <v>0.258480048</v>
+        <v>0.25771116</v>
       </c>
       <c r="P56">
-        <v>1.033920192</v>
+        <v>1.03084464</v>
       </c>
       <c r="Q56">
-        <v>1.113920192</v>
+        <v>1.11084464</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2146508605383063</v>
+        <v>0.218016099413011</v>
       </c>
       <c r="T56">
-        <v>1.848986130797244</v>
+        <v>1.88583687580566</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.22544187912356</v>
+        <v>7.094070208594039</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.121999244735855</v>
+        <v>0.121801493624089</v>
       </c>
       <c r="C57">
-        <v>3.544898969557646</v>
+        <v>3.480335400143584</v>
       </c>
       <c r="D57">
-        <v>5.338898969557647</v>
+        <v>5.345135400143584</v>
       </c>
       <c r="E57">
-        <v>2.484000000000001</v>
+        <v>2.5548</v>
       </c>
       <c r="F57">
-        <v>3.894000000000001</v>
+        <v>3.9648</v>
       </c>
       <c r="G57">
         <v>2.1</v>
@@ -5961,28 +5961,28 @@
         <v>1.5</v>
       </c>
       <c r="M57">
-        <v>0.2114442</v>
+        <v>0.21528864</v>
       </c>
       <c r="N57">
-        <v>1.2885558</v>
+        <v>1.28471136</v>
       </c>
       <c r="O57">
-        <v>0.25771116</v>
+        <v>0.256942272</v>
       </c>
       <c r="P57">
-        <v>1.03084464</v>
+        <v>1.027769088</v>
       </c>
       <c r="Q57">
-        <v>1.11084464</v>
+        <v>1.107769088</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.218016099413011</v>
+        <v>0.2215343036911114</v>
       </c>
       <c r="T57">
-        <v>1.88583687580566</v>
+        <v>1.924362654678094</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.094070208594039</v>
+        <v>6.967390383440574</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.121801493624089</v>
+        <v>0.121603742512323</v>
       </c>
       <c r="C58">
-        <v>3.480335400143584</v>
+        <v>3.415786417464071</v>
       </c>
       <c r="D58">
-        <v>5.345135400143584</v>
+        <v>5.351386417464072</v>
       </c>
       <c r="E58">
-        <v>2.5548</v>
+        <v>2.6256</v>
       </c>
       <c r="F58">
-        <v>3.9648</v>
+        <v>4.035600000000001</v>
       </c>
       <c r="G58">
         <v>2.1</v>
@@ -6043,28 +6043,28 @@
         <v>1.5</v>
       </c>
       <c r="M58">
-        <v>0.21528864</v>
+        <v>0.21913308</v>
       </c>
       <c r="N58">
-        <v>1.28471136</v>
+        <v>1.28086692</v>
       </c>
       <c r="O58">
-        <v>0.256942272</v>
+        <v>0.256173384</v>
       </c>
       <c r="P58">
-        <v>1.027769088</v>
+        <v>1.024693536</v>
       </c>
       <c r="Q58">
-        <v>1.107769088</v>
+        <v>1.104693536</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2215343036911114</v>
+        <v>0.2252161453774954</v>
       </c>
       <c r="T58">
-        <v>1.924362654678094</v>
+        <v>1.96468033024227</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.967390383440574</v>
+        <v>6.845155464432845</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.121603742512323</v>
+        <v>0.1214059914005571</v>
       </c>
       <c r="C59">
-        <v>3.415786417464071</v>
+        <v>3.351252072755619</v>
       </c>
       <c r="D59">
-        <v>5.351386417464072</v>
+        <v>5.357652072755619</v>
       </c>
       <c r="E59">
-        <v>2.6256</v>
+        <v>2.696400000000001</v>
       </c>
       <c r="F59">
-        <v>4.035600000000001</v>
+        <v>4.106400000000001</v>
       </c>
       <c r="G59">
         <v>2.1</v>
@@ -6125,28 +6125,28 @@
         <v>1.5</v>
       </c>
       <c r="M59">
-        <v>0.21913308</v>
+        <v>0.22297752</v>
       </c>
       <c r="N59">
-        <v>1.28086692</v>
+        <v>1.27702248</v>
       </c>
       <c r="O59">
-        <v>0.256173384</v>
+        <v>0.255404496</v>
       </c>
       <c r="P59">
-        <v>1.024693536</v>
+        <v>1.021617984</v>
       </c>
       <c r="Q59">
-        <v>1.104693536</v>
+        <v>1.101617984</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2252161453774954</v>
+        <v>0.2290733128584692</v>
       </c>
       <c r="T59">
-        <v>1.96468033024227</v>
+        <v>2.006917895119025</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.845155464432845</v>
+        <v>6.727135542632278</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1214059914005571</v>
+        <v>0.1212082402887911</v>
       </c>
       <c r="C60">
-        <v>3.35125207275562</v>
+        <v>3.286732417494973</v>
       </c>
       <c r="D60">
-        <v>5.357652072755619</v>
+        <v>5.363932417494974</v>
       </c>
       <c r="E60">
-        <v>2.6964</v>
+        <v>2.7672</v>
       </c>
       <c r="F60">
-        <v>4.1064</v>
+        <v>4.1772</v>
       </c>
       <c r="G60">
         <v>2.1</v>
@@ -6207,28 +6207,28 @@
         <v>1.5</v>
       </c>
       <c r="M60">
-        <v>0.22297752</v>
+        <v>0.22682196</v>
       </c>
       <c r="N60">
-        <v>1.27702248</v>
+        <v>1.27317804</v>
       </c>
       <c r="O60">
-        <v>0.255404496</v>
+        <v>0.254635608</v>
       </c>
       <c r="P60">
-        <v>1.021617984</v>
+        <v>1.018542432</v>
       </c>
       <c r="Q60">
-        <v>1.101617984</v>
+        <v>1.098542432</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2290733128584691</v>
+        <v>0.23311863485071</v>
       </c>
       <c r="T60">
-        <v>2.006917895119024</v>
+        <v>2.051215829014158</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.72713554263228</v>
+        <v>6.613116296146986</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1212082402887911</v>
+        <v>0.1210104891770251</v>
       </c>
       <c r="C61">
-        <v>3.286732417494973</v>
+        <v>3.222227503400538</v>
       </c>
       <c r="D61">
-        <v>5.363932417494974</v>
+        <v>5.370227503400538</v>
       </c>
       <c r="E61">
-        <v>2.7672</v>
+        <v>2.838</v>
       </c>
       <c r="F61">
-        <v>4.1772</v>
+        <v>4.248</v>
       </c>
       <c r="G61">
         <v>2.1</v>
@@ -6289,28 +6289,28 @@
         <v>1.5</v>
       </c>
       <c r="M61">
-        <v>0.22682196</v>
+        <v>0.2306664</v>
       </c>
       <c r="N61">
-        <v>1.27317804</v>
+        <v>1.2693336</v>
       </c>
       <c r="O61">
-        <v>0.254635608</v>
+        <v>0.25386672</v>
       </c>
       <c r="P61">
-        <v>1.018542432</v>
+        <v>1.01546688</v>
       </c>
       <c r="Q61">
-        <v>1.098542432</v>
+        <v>1.09546688</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.23311863485071</v>
+        <v>0.2373662229425628</v>
       </c>
       <c r="T61">
-        <v>2.051215829014158</v>
+        <v>2.097728659604049</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.613116296146986</v>
+        <v>6.502897691211203</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1210104891770251</v>
+        <v>0.1208127380652592</v>
       </c>
       <c r="C62">
-        <v>3.222227503400538</v>
+        <v>3.157737382433785</v>
       </c>
       <c r="D62">
-        <v>5.370227503400538</v>
+        <v>5.376537382433784</v>
       </c>
       <c r="E62">
-        <v>2.838</v>
+        <v>2.908799999999999</v>
       </c>
       <c r="F62">
-        <v>4.248</v>
+        <v>4.3188</v>
       </c>
       <c r="G62">
         <v>2.1</v>
@@ -6371,28 +6371,28 @@
         <v>1.5</v>
       </c>
       <c r="M62">
-        <v>0.2306664</v>
+        <v>0.23451084</v>
       </c>
       <c r="N62">
-        <v>1.2693336</v>
+        <v>1.26548916</v>
       </c>
       <c r="O62">
-        <v>0.25386672</v>
+        <v>0.253097832</v>
       </c>
       <c r="P62">
-        <v>1.01546688</v>
+        <v>1.012391328</v>
       </c>
       <c r="Q62">
-        <v>1.09546688</v>
+        <v>1.092391328</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2373662229425628</v>
+        <v>0.2418316360647671</v>
       </c>
       <c r="T62">
-        <v>2.097728659604049</v>
+        <v>2.146626763557523</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.502897691211203</v>
+        <v>6.396292811027414</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1208127380652592</v>
+        <v>0.1206149869534932</v>
       </c>
       <c r="C63">
-        <v>3.157737382433785</v>
+        <v>3.093262106800685</v>
       </c>
       <c r="D63">
-        <v>5.376537382433784</v>
+        <v>5.382862106800684</v>
       </c>
       <c r="E63">
-        <v>2.908799999999999</v>
+        <v>2.9796</v>
       </c>
       <c r="F63">
-        <v>4.3188</v>
+        <v>4.3896</v>
       </c>
       <c r="G63">
         <v>2.1</v>
@@ -6453,28 +6453,28 @@
         <v>1.5</v>
       </c>
       <c r="M63">
-        <v>0.23451084</v>
+        <v>0.23835528</v>
       </c>
       <c r="N63">
-        <v>1.26548916</v>
+        <v>1.26164472</v>
       </c>
       <c r="O63">
-        <v>0.253097832</v>
+        <v>0.252328944</v>
       </c>
       <c r="P63">
-        <v>1.012391328</v>
+        <v>1.009315776</v>
       </c>
       <c r="Q63">
-        <v>1.092391328</v>
+        <v>1.089315776</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2418316360647671</v>
+        <v>0.2465320709302452</v>
       </c>
       <c r="T63">
-        <v>2.146626763557523</v>
+        <v>2.198098451929601</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.396292811027414</v>
+        <v>6.293126797946326</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1206149869534932</v>
+        <v>0.1204172358417272</v>
       </c>
       <c r="C64">
-        <v>3.093262106800685</v>
+        <v>3.028801728953153</v>
       </c>
       <c r="D64">
-        <v>5.382862106800684</v>
+        <v>5.389201728953153</v>
       </c>
       <c r="E64">
-        <v>2.9796</v>
+        <v>3.0504</v>
       </c>
       <c r="F64">
-        <v>4.3896</v>
+        <v>4.4604</v>
       </c>
       <c r="G64">
         <v>2.1</v>
@@ -6535,28 +6535,28 @@
         <v>1.5</v>
       </c>
       <c r="M64">
-        <v>0.23835528</v>
+        <v>0.24219972</v>
       </c>
       <c r="N64">
-        <v>1.26164472</v>
+        <v>1.25780028</v>
       </c>
       <c r="O64">
-        <v>0.252328944</v>
+        <v>0.251560056</v>
       </c>
       <c r="P64">
-        <v>1.009315776</v>
+        <v>1.006240224</v>
       </c>
       <c r="Q64">
-        <v>1.089315776</v>
+        <v>1.086240224</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2465320709302452</v>
+        <v>0.2514865833560195</v>
       </c>
       <c r="T64">
-        <v>2.198098451929601</v>
+        <v>2.252352393727197</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.293126797946326</v>
+        <v>6.193235896391623</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1204172358417272</v>
+        <v>0.1207314847299613</v>
       </c>
       <c r="C65">
-        <v>3.028801728953153</v>
+        <v>2.947934328928604</v>
       </c>
       <c r="D65">
-        <v>5.389201728953153</v>
+        <v>5.379134328928603</v>
       </c>
       <c r="E65">
-        <v>3.0504</v>
+        <v>3.1212</v>
       </c>
       <c r="F65">
-        <v>4.4604</v>
+        <v>4.5312</v>
       </c>
       <c r="G65">
         <v>2.1</v>
@@ -6617,45 +6617,45 @@
         <v>1.5</v>
       </c>
       <c r="M65">
-        <v>0.24219972</v>
+        <v>0.25057536</v>
       </c>
       <c r="N65">
-        <v>1.25780028</v>
+        <v>1.24942464</v>
       </c>
       <c r="O65">
-        <v>0.251560056</v>
+        <v>0.249884928</v>
       </c>
       <c r="P65">
-        <v>1.006240224</v>
+        <v>0.999539712</v>
       </c>
       <c r="Q65">
-        <v>1.086240224</v>
+        <v>1.079539712</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2514865833560195</v>
+        <v>0.2567163464721146</v>
       </c>
       <c r="T65">
-        <v>2.252352393727197</v>
+        <v>2.309620443402438</v>
       </c>
       <c r="U65">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>6.193235896391623</v>
+        <v>5.986223066785177</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1207314847299613</v>
+        <v>0.1205417336181953</v>
       </c>
       <c r="C66">
-        <v>2.947934328928604</v>
+        <v>2.88320876559458</v>
       </c>
       <c r="D66">
-        <v>5.379134328928603</v>
+        <v>5.385208765594579</v>
       </c>
       <c r="E66">
-        <v>3.1212</v>
+        <v>3.192</v>
       </c>
       <c r="F66">
-        <v>4.5312</v>
+        <v>4.602</v>
       </c>
       <c r="G66">
         <v>2.1</v>
@@ -6699,28 +6699,28 @@
         <v>1.5</v>
       </c>
       <c r="M66">
-        <v>0.25057536</v>
+        <v>0.2544906</v>
       </c>
       <c r="N66">
-        <v>1.24942464</v>
+        <v>1.2455094</v>
       </c>
       <c r="O66">
-        <v>0.249884928</v>
+        <v>0.24910188</v>
       </c>
       <c r="P66">
-        <v>0.999539712</v>
+        <v>0.99640752</v>
       </c>
       <c r="Q66">
-        <v>1.079539712</v>
+        <v>1.07640752</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2567163464721146</v>
+        <v>0.2622449531948437</v>
       </c>
       <c r="T66">
-        <v>2.309620443402438</v>
+        <v>2.37016095305912</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.986223066785177</v>
+        <v>5.894127327296175</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1205417336181953</v>
+        <v>0.1203519825064293</v>
       </c>
       <c r="C67">
-        <v>2.88320876559458</v>
+        <v>2.818496936997017</v>
       </c>
       <c r="D67">
-        <v>5.385208765594579</v>
+        <v>5.391296936997017</v>
       </c>
       <c r="E67">
-        <v>3.192</v>
+        <v>3.2628</v>
       </c>
       <c r="F67">
-        <v>4.602</v>
+        <v>4.672800000000001</v>
       </c>
       <c r="G67">
         <v>2.1</v>
@@ -6781,28 +6781,28 @@
         <v>1.5</v>
       </c>
       <c r="M67">
-        <v>0.2544906</v>
+        <v>0.2584058400000001</v>
       </c>
       <c r="N67">
-        <v>1.2455094</v>
+        <v>1.24159416</v>
       </c>
       <c r="O67">
-        <v>0.24910188</v>
+        <v>0.248318832</v>
       </c>
       <c r="P67">
-        <v>0.99640752</v>
+        <v>0.993275328</v>
       </c>
       <c r="Q67">
-        <v>1.07640752</v>
+        <v>1.073275328</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2622449531948437</v>
+        <v>0.2680987720777333</v>
       </c>
       <c r="T67">
-        <v>2.37016095305912</v>
+        <v>2.434262669166196</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.894127327296175</v>
+        <v>5.804822367791687</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1203519825064293</v>
+        <v>0.1201622313946634</v>
       </c>
       <c r="C68">
-        <v>2.818496936997017</v>
+        <v>2.753798889771472</v>
       </c>
       <c r="D68">
-        <v>5.391296936997017</v>
+        <v>5.397398889771473</v>
       </c>
       <c r="E68">
-        <v>3.2628</v>
+        <v>3.333600000000001</v>
       </c>
       <c r="F68">
-        <v>4.672800000000001</v>
+        <v>4.743600000000001</v>
       </c>
       <c r="G68">
         <v>2.1</v>
@@ -6863,28 +6863,28 @@
         <v>1.5</v>
       </c>
       <c r="M68">
-        <v>0.2584058400000001</v>
+        <v>0.26232108</v>
       </c>
       <c r="N68">
-        <v>1.24159416</v>
+        <v>1.23767892</v>
       </c>
       <c r="O68">
-        <v>0.248318832</v>
+        <v>0.247535784</v>
       </c>
       <c r="P68">
-        <v>0.993275328</v>
+        <v>0.990143136</v>
       </c>
       <c r="Q68">
-        <v>1.073275328</v>
+        <v>1.070143136</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2680987720777333</v>
+        <v>0.2743073678626163</v>
       </c>
       <c r="T68">
-        <v>2.434262669166196</v>
+        <v>2.50224933776461</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.804822367791687</v>
+        <v>5.718183227973901</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1201622313946634</v>
+        <v>0.1199724802828974</v>
       </c>
       <c r="C69">
-        <v>2.753798889771472</v>
+        <v>2.689114670764881</v>
       </c>
       <c r="D69">
-        <v>5.397398889771473</v>
+        <v>5.40351467076488</v>
       </c>
       <c r="E69">
-        <v>3.333600000000001</v>
+        <v>3.4044</v>
       </c>
       <c r="F69">
-        <v>4.743600000000001</v>
+        <v>4.8144</v>
       </c>
       <c r="G69">
         <v>2.1</v>
@@ -6945,28 +6945,28 @@
         <v>1.5</v>
       </c>
       <c r="M69">
-        <v>0.26232108</v>
+        <v>0.26623632</v>
       </c>
       <c r="N69">
-        <v>1.23767892</v>
+        <v>1.23376368</v>
       </c>
       <c r="O69">
-        <v>0.247535784</v>
+        <v>0.246752736</v>
       </c>
       <c r="P69">
-        <v>0.990143136</v>
+        <v>0.987010944</v>
       </c>
       <c r="Q69">
-        <v>1.070143136</v>
+        <v>1.067010944</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2743073678626163</v>
+        <v>0.2809040008840544</v>
       </c>
       <c r="T69">
-        <v>2.50224933776461</v>
+        <v>2.574485173150423</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.718183227973901</v>
+        <v>5.634092298150756</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1199724802828974</v>
+        <v>0.1197827291711314</v>
       </c>
       <c r="C70">
-        <v>2.689114670764881</v>
+        <v>2.624444327036735</v>
       </c>
       <c r="D70">
-        <v>5.40351467076488</v>
+        <v>5.409644327036735</v>
       </c>
       <c r="E70">
-        <v>3.4044</v>
+        <v>3.4752</v>
       </c>
       <c r="F70">
-        <v>4.8144</v>
+        <v>4.8852</v>
       </c>
       <c r="G70">
         <v>2.1</v>
@@ -7027,28 +7027,28 @@
         <v>1.5</v>
       </c>
       <c r="M70">
-        <v>0.26623632</v>
+        <v>0.27015156</v>
       </c>
       <c r="N70">
-        <v>1.23376368</v>
+        <v>1.22984844</v>
       </c>
       <c r="O70">
-        <v>0.246752736</v>
+        <v>0.245969688</v>
       </c>
       <c r="P70">
-        <v>0.987010944</v>
+        <v>0.9838787520000001</v>
       </c>
       <c r="Q70">
-        <v>1.067010944</v>
+        <v>1.063878752</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2809040008840544</v>
+        <v>0.2879262231326821</v>
       </c>
       <c r="T70">
-        <v>2.574485173150423</v>
+        <v>2.651381385012742</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.634092298150756</v>
+        <v>5.552438786583354</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1197827291711314</v>
+        <v>0.1195929780593654</v>
       </c>
       <c r="C71">
-        <v>2.624444327036735</v>
+        <v>2.559787905860309</v>
       </c>
       <c r="D71">
-        <v>5.409644327036735</v>
+        <v>5.415787905860308</v>
       </c>
       <c r="E71">
-        <v>3.4752</v>
+        <v>3.546</v>
       </c>
       <c r="F71">
-        <v>4.8852</v>
+        <v>4.956</v>
       </c>
       <c r="G71">
         <v>2.1</v>
@@ -7109,28 +7109,28 @@
         <v>1.5</v>
       </c>
       <c r="M71">
-        <v>0.27015156</v>
+        <v>0.2740668000000001</v>
       </c>
       <c r="N71">
-        <v>1.22984844</v>
+        <v>1.2259332</v>
       </c>
       <c r="O71">
-        <v>0.245969688</v>
+        <v>0.24518664</v>
       </c>
       <c r="P71">
-        <v>0.9838787520000001</v>
+        <v>0.98074656</v>
       </c>
       <c r="Q71">
-        <v>1.063878752</v>
+        <v>1.06074656</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2879262231326821</v>
+        <v>0.2954165935312182</v>
       </c>
       <c r="T71">
-        <v>2.651381385012742</v>
+        <v>2.733404010999215</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.552438786583354</v>
+        <v>5.473118232489305</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1195929780593654</v>
+        <v>0.1194032269475995</v>
       </c>
       <c r="C72">
-        <v>2.559787905860309</v>
+        <v>2.495145454723867</v>
       </c>
       <c r="D72">
-        <v>5.415787905860308</v>
+        <v>5.421945454723868</v>
       </c>
       <c r="E72">
-        <v>3.546</v>
+        <v>3.6168</v>
       </c>
       <c r="F72">
-        <v>4.956</v>
+        <v>5.026800000000001</v>
       </c>
       <c r="G72">
         <v>2.1</v>
@@ -7191,28 +7191,28 @@
         <v>1.5</v>
       </c>
       <c r="M72">
-        <v>0.2740668000000001</v>
+        <v>0.27798204</v>
       </c>
       <c r="N72">
-        <v>1.2259332</v>
+        <v>1.22201796</v>
       </c>
       <c r="O72">
-        <v>0.24518664</v>
+        <v>0.244403592</v>
       </c>
       <c r="P72">
-        <v>0.98074656</v>
+        <v>0.977614368</v>
       </c>
       <c r="Q72">
-        <v>1.06074656</v>
+        <v>1.057614368</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2954165935312182</v>
+        <v>0.303423541198619</v>
       </c>
       <c r="T72">
-        <v>2.733404010999215</v>
+        <v>2.821083369812342</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.473118232489305</v>
+        <v>5.396032060200723</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1194032269475995</v>
+        <v>0.1192134758358335</v>
       </c>
       <c r="C73">
-        <v>2.495145454723868</v>
+        <v>2.4305170213319</v>
       </c>
       <c r="D73">
-        <v>5.421945454723868</v>
+        <v>5.428117021331899</v>
       </c>
       <c r="E73">
-        <v>3.6168</v>
+        <v>3.6876</v>
       </c>
       <c r="F73">
-        <v>5.0268</v>
+        <v>5.0976</v>
       </c>
       <c r="G73">
         <v>2.1</v>
@@ -7273,28 +7273,28 @@
         <v>1.5</v>
       </c>
       <c r="M73">
-        <v>0.27798204</v>
+        <v>0.28189728</v>
       </c>
       <c r="N73">
-        <v>1.22201796</v>
+        <v>1.21810272</v>
       </c>
       <c r="O73">
-        <v>0.244403592</v>
+        <v>0.243620544</v>
       </c>
       <c r="P73">
-        <v>0.977614368</v>
+        <v>0.9744821760000001</v>
       </c>
       <c r="Q73">
-        <v>1.057614368</v>
+        <v>1.054482176</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3034235411986189</v>
+        <v>0.3120024136994055</v>
       </c>
       <c r="T73">
-        <v>2.821083369812341</v>
+        <v>2.915025539969262</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.396032060200724</v>
+        <v>5.321087170475714</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1192134758358335</v>
+        <v>0.1190237247240676</v>
       </c>
       <c r="C74">
-        <v>2.4305170213319</v>
+        <v>2.365902653606327</v>
       </c>
       <c r="D74">
-        <v>5.428117021331899</v>
+        <v>5.434302653606327</v>
       </c>
       <c r="E74">
-        <v>3.6876</v>
+        <v>3.7584</v>
       </c>
       <c r="F74">
-        <v>5.0976</v>
+        <v>5.1684</v>
       </c>
       <c r="G74">
         <v>2.1</v>
@@ -7355,28 +7355,28 @@
         <v>1.5</v>
       </c>
       <c r="M74">
-        <v>0.28189728</v>
+        <v>0.28581252</v>
       </c>
       <c r="N74">
-        <v>1.21810272</v>
+        <v>1.21418748</v>
       </c>
       <c r="O74">
-        <v>0.243620544</v>
+        <v>0.242837496</v>
       </c>
       <c r="P74">
-        <v>0.9744821760000001</v>
+        <v>0.9713499840000001</v>
       </c>
       <c r="Q74">
-        <v>1.054482176</v>
+        <v>1.051349984</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3120024136994055</v>
+        <v>0.3212167582372872</v>
       </c>
       <c r="T74">
-        <v>2.915025539969262</v>
+        <v>3.015926389397066</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.321087170475714</v>
+        <v>5.248195565400704</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1190237247240676</v>
+        <v>0.1188339736123016</v>
       </c>
       <c r="C75">
-        <v>2.365902653606327</v>
+        <v>2.301302399687767</v>
       </c>
       <c r="D75">
-        <v>5.434302653606327</v>
+        <v>5.440502399687768</v>
       </c>
       <c r="E75">
-        <v>3.7584</v>
+        <v>3.8292</v>
       </c>
       <c r="F75">
-        <v>5.1684</v>
+        <v>5.2392</v>
       </c>
       <c r="G75">
         <v>2.1</v>
@@ -7437,28 +7437,28 @@
         <v>1.5</v>
       </c>
       <c r="M75">
-        <v>0.28581252</v>
+        <v>0.28972776</v>
       </c>
       <c r="N75">
-        <v>1.21418748</v>
+        <v>1.21027224</v>
       </c>
       <c r="O75">
-        <v>0.242837496</v>
+        <v>0.242054448</v>
       </c>
       <c r="P75">
-        <v>0.9713499840000001</v>
+        <v>0.9682177920000001</v>
       </c>
       <c r="Q75">
-        <v>1.051349984</v>
+        <v>1.048217792</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3212167582372872</v>
+        <v>0.3311398985088523</v>
       </c>
       <c r="T75">
-        <v>3.015926389397066</v>
+        <v>3.124588842627009</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.248195565400704</v>
+        <v>5.1772740037061</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1188339736123016</v>
+        <v>0.1186442225005356</v>
       </c>
       <c r="C76">
-        <v>2.301302399687767</v>
+        <v>2.236716307936776</v>
       </c>
       <c r="D76">
-        <v>5.440502399687768</v>
+        <v>5.446716307936777</v>
       </c>
       <c r="E76">
-        <v>3.8292</v>
+        <v>3.9</v>
       </c>
       <c r="F76">
-        <v>5.2392</v>
+        <v>5.31</v>
       </c>
       <c r="G76">
         <v>2.1</v>
@@ -7519,28 +7519,28 @@
         <v>1.5</v>
       </c>
       <c r="M76">
-        <v>0.28972776</v>
+        <v>0.293643</v>
       </c>
       <c r="N76">
-        <v>1.21027224</v>
+        <v>1.206357</v>
       </c>
       <c r="O76">
-        <v>0.242054448</v>
+        <v>0.2412714</v>
       </c>
       <c r="P76">
-        <v>0.9682177920000001</v>
+        <v>0.9650855999999999</v>
       </c>
       <c r="Q76">
-        <v>1.048217792</v>
+        <v>1.0450856</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3311398985088523</v>
+        <v>0.3418568900021425</v>
       </c>
       <c r="T76">
-        <v>3.124588842627009</v>
+        <v>3.241944292115348</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.1772740037061</v>
+        <v>5.108243683656684</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1186442225005356</v>
+        <v>0.1184544713887697</v>
       </c>
       <c r="C77">
-        <v>2.236716307936776</v>
+        <v>2.172144426935101</v>
       </c>
       <c r="D77">
-        <v>5.446716307936777</v>
+        <v>5.4529444269351</v>
       </c>
       <c r="E77">
-        <v>3.9</v>
+        <v>3.9708</v>
       </c>
       <c r="F77">
-        <v>5.31</v>
+        <v>5.3808</v>
       </c>
       <c r="G77">
         <v>2.1</v>
@@ -7601,28 +7601,28 @@
         <v>1.5</v>
       </c>
       <c r="M77">
-        <v>0.293643</v>
+        <v>0.29755824</v>
       </c>
       <c r="N77">
-        <v>1.206357</v>
+        <v>1.20244176</v>
       </c>
       <c r="O77">
-        <v>0.2412714</v>
+        <v>0.240488352</v>
       </c>
       <c r="P77">
-        <v>0.9650855999999999</v>
+        <v>0.9619534080000001</v>
       </c>
       <c r="Q77">
-        <v>1.0450856</v>
+        <v>1.041953408</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3418568900021425</v>
+        <v>0.3534669641198736</v>
       </c>
       <c r="T77">
-        <v>3.241944292115348</v>
+        <v>3.369079362394381</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.108243683656684</v>
+        <v>5.041029950976993</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1184544713887697</v>
+        <v>0.1182647202770037</v>
       </c>
       <c r="C78">
-        <v>2.172144426935101</v>
+        <v>2.107586805486945</v>
       </c>
       <c r="D78">
-        <v>5.4529444269351</v>
+        <v>5.459186805486945</v>
       </c>
       <c r="E78">
-        <v>3.9708</v>
+        <v>4.0416</v>
       </c>
       <c r="F78">
-        <v>5.3808</v>
+        <v>5.4516</v>
       </c>
       <c r="G78">
         <v>2.1</v>
@@ -7683,28 +7683,28 @@
         <v>1.5</v>
       </c>
       <c r="M78">
-        <v>0.29755824</v>
+        <v>0.30147348</v>
       </c>
       <c r="N78">
-        <v>1.20244176</v>
+        <v>1.19852652</v>
       </c>
       <c r="O78">
-        <v>0.240488352</v>
+        <v>0.239705304</v>
       </c>
       <c r="P78">
-        <v>0.9619534080000001</v>
+        <v>0.9588212159999999</v>
       </c>
       <c r="Q78">
-        <v>1.041953408</v>
+        <v>1.038821216</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3534669641198736</v>
+        <v>0.3660866099000161</v>
       </c>
       <c r="T78">
-        <v>3.369079362394381</v>
+        <v>3.507269656175939</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.041029950976993</v>
+        <v>4.975562029535732</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1182647202770037</v>
+        <v>0.1180749691652377</v>
       </c>
       <c r="C79">
-        <v>2.107586805486945</v>
+        <v>2.043043492620254</v>
       </c>
       <c r="D79">
-        <v>5.459186805486945</v>
+        <v>5.465443492620254</v>
       </c>
       <c r="E79">
-        <v>4.0416</v>
+        <v>4.1124</v>
       </c>
       <c r="F79">
-        <v>5.4516</v>
+        <v>5.5224</v>
       </c>
       <c r="G79">
         <v>2.1</v>
@@ -7765,28 +7765,28 @@
         <v>1.5</v>
       </c>
       <c r="M79">
-        <v>0.30147348</v>
+        <v>0.30538872</v>
       </c>
       <c r="N79">
-        <v>1.19852652</v>
+        <v>1.19461128</v>
       </c>
       <c r="O79">
-        <v>0.239705304</v>
+        <v>0.238922256</v>
       </c>
       <c r="P79">
-        <v>0.9588212159999999</v>
+        <v>0.955689024</v>
       </c>
       <c r="Q79">
-        <v>1.038821216</v>
+        <v>1.035689024</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3660866099000161</v>
+        <v>0.3798534962056261</v>
       </c>
       <c r="T79">
-        <v>3.507269656175939</v>
+        <v>3.658022703937639</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.975562029535732</v>
+        <v>4.911772772746812</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1180749691652377</v>
+        <v>0.1178852180534718</v>
       </c>
       <c r="C80">
-        <v>2.043043492620254</v>
+        <v>1.978514537587986</v>
       </c>
       <c r="D80">
-        <v>5.465443492620254</v>
+        <v>5.471714537587987</v>
       </c>
       <c r="E80">
-        <v>4.1124</v>
+        <v>4.1832</v>
       </c>
       <c r="F80">
-        <v>5.5224</v>
+        <v>5.5932</v>
       </c>
       <c r="G80">
         <v>2.1</v>
@@ -7847,28 +7847,28 @@
         <v>1.5</v>
       </c>
       <c r="M80">
-        <v>0.30538872</v>
+        <v>0.30930396</v>
       </c>
       <c r="N80">
-        <v>1.19461128</v>
+        <v>1.19069604</v>
       </c>
       <c r="O80">
-        <v>0.238922256</v>
+        <v>0.238139208</v>
       </c>
       <c r="P80">
-        <v>0.955689024</v>
+        <v>0.952556832</v>
       </c>
       <c r="Q80">
-        <v>1.035689024</v>
+        <v>1.032556832</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3798534962056261</v>
+        <v>0.3949315145403418</v>
       </c>
       <c r="T80">
-        <v>3.658022703937639</v>
+        <v>3.8231331848195</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.911772772746812</v>
+        <v>4.849598433851282</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1178852180534718</v>
+        <v>0.1176954669417058</v>
       </c>
       <c r="C81">
-        <v>1.978514537587986</v>
+        <v>1.913999989869416</v>
       </c>
       <c r="D81">
-        <v>5.471714537587987</v>
+        <v>5.477999989869416</v>
       </c>
       <c r="E81">
-        <v>4.1832</v>
+        <v>4.254</v>
       </c>
       <c r="F81">
-        <v>5.5932</v>
+        <v>5.664000000000001</v>
       </c>
       <c r="G81">
         <v>2.1</v>
@@ -7929,28 +7929,28 @@
         <v>1.5</v>
       </c>
       <c r="M81">
-        <v>0.30930396</v>
+        <v>0.3132192</v>
       </c>
       <c r="N81">
-        <v>1.19069604</v>
+        <v>1.1867808</v>
       </c>
       <c r="O81">
-        <v>0.238139208</v>
+        <v>0.23735616</v>
       </c>
       <c r="P81">
-        <v>0.952556832</v>
+        <v>0.9494246399999999</v>
       </c>
       <c r="Q81">
-        <v>1.032556832</v>
+        <v>1.02942464</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3949315145403418</v>
+        <v>0.4115173347085291</v>
       </c>
       <c r="T81">
-        <v>3.8231331848195</v>
+        <v>4.004754713789549</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.849598433851282</v>
+        <v>4.788978453428141</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1176954669417058</v>
+        <v>0.1175057158299398</v>
       </c>
       <c r="C82">
-        <v>1.913999989869416</v>
+        <v>1.849499899171424</v>
       </c>
       <c r="D82">
-        <v>5.477999989869416</v>
+        <v>5.484299899171425</v>
       </c>
       <c r="E82">
-        <v>4.254</v>
+        <v>4.324800000000001</v>
       </c>
       <c r="F82">
-        <v>5.664000000000001</v>
+        <v>5.734800000000001</v>
       </c>
       <c r="G82">
         <v>2.1</v>
@@ -8011,28 +8011,28 @@
         <v>1.5</v>
       </c>
       <c r="M82">
-        <v>0.3132192</v>
+        <v>0.3171344400000001</v>
       </c>
       <c r="N82">
-        <v>1.1867808</v>
+        <v>1.18286556</v>
       </c>
       <c r="O82">
-        <v>0.23735616</v>
+        <v>0.236573112</v>
       </c>
       <c r="P82">
-        <v>0.9494246399999999</v>
+        <v>0.946292448</v>
       </c>
       <c r="Q82">
-        <v>1.02942464</v>
+        <v>1.026292448</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4115173347085291</v>
+        <v>0.429849030683894</v>
       </c>
       <c r="T82">
-        <v>4.004754713789549</v>
+        <v>4.205494298440654</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.788978453428141</v>
+        <v>4.729855262645078</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1175057158299398</v>
+        <v>0.1173159647181738</v>
       </c>
       <c r="C83">
-        <v>1.849499899171424</v>
+        <v>1.785014315429823</v>
       </c>
       <c r="D83">
-        <v>5.484299899171425</v>
+        <v>5.490614315429823</v>
       </c>
       <c r="E83">
-        <v>4.324800000000001</v>
+        <v>4.3956</v>
       </c>
       <c r="F83">
-        <v>5.734800000000001</v>
+        <v>5.8056</v>
       </c>
       <c r="G83">
         <v>2.1</v>
@@ -8093,28 +8093,28 @@
         <v>1.5</v>
       </c>
       <c r="M83">
-        <v>0.3171344400000001</v>
+        <v>0.32104968</v>
       </c>
       <c r="N83">
-        <v>1.18286556</v>
+        <v>1.17895032</v>
       </c>
       <c r="O83">
-        <v>0.236573112</v>
+        <v>0.235790064</v>
       </c>
       <c r="P83">
-        <v>0.946292448</v>
+        <v>0.943160256</v>
       </c>
       <c r="Q83">
-        <v>1.026292448</v>
+        <v>1.023160256</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.429849030683894</v>
+        <v>0.4502175817676327</v>
       </c>
       <c r="T83">
-        <v>4.205494298440654</v>
+        <v>4.428538281386325</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.729855262645078</v>
+        <v>4.672174100905504</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1173159647181738</v>
+        <v>0.1171262136064079</v>
       </c>
       <c r="C84">
-        <v>1.785014315429823</v>
+        <v>1.720543288810651</v>
       </c>
       <c r="D84">
-        <v>5.490614315429823</v>
+        <v>5.496943288810652</v>
       </c>
       <c r="E84">
-        <v>4.3956</v>
+        <v>4.4664</v>
       </c>
       <c r="F84">
-        <v>5.8056</v>
+        <v>5.8764</v>
       </c>
       <c r="G84">
         <v>2.1</v>
@@ -8175,28 +8175,28 @@
         <v>1.5</v>
       </c>
       <c r="M84">
-        <v>0.32104968</v>
+        <v>0.32496492</v>
       </c>
       <c r="N84">
-        <v>1.17895032</v>
+        <v>1.17503508</v>
       </c>
       <c r="O84">
-        <v>0.235790064</v>
+        <v>0.235007016</v>
       </c>
       <c r="P84">
-        <v>0.943160256</v>
+        <v>0.9400280640000001</v>
       </c>
       <c r="Q84">
-        <v>1.023160256</v>
+        <v>1.020028064</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4502175817676327</v>
+        <v>0.4729824329788701</v>
       </c>
       <c r="T84">
-        <v>4.428538281386325</v>
+        <v>4.677822732913842</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.672174100905504</v>
+        <v>4.615882846677727</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1171262136064079</v>
+        <v>0.1169364624946419</v>
       </c>
       <c r="C85">
-        <v>1.720543288810651</v>
+        <v>1.656086869711535</v>
       </c>
       <c r="D85">
-        <v>5.496943288810652</v>
+        <v>5.503286869711535</v>
       </c>
       <c r="E85">
-        <v>4.4664</v>
+        <v>4.5372</v>
       </c>
       <c r="F85">
-        <v>5.8764</v>
+        <v>5.9472</v>
       </c>
       <c r="G85">
         <v>2.1</v>
@@ -8257,28 +8257,28 @@
         <v>1.5</v>
       </c>
       <c r="M85">
-        <v>0.32496492</v>
+        <v>0.32888016</v>
       </c>
       <c r="N85">
-        <v>1.17503508</v>
+        <v>1.17111984</v>
       </c>
       <c r="O85">
-        <v>0.235007016</v>
+        <v>0.234223968</v>
       </c>
       <c r="P85">
-        <v>0.9400280640000001</v>
+        <v>0.936895872</v>
       </c>
       <c r="Q85">
-        <v>1.020028064</v>
+        <v>1.016895872</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4729824329788701</v>
+        <v>0.4985928905915123</v>
       </c>
       <c r="T85">
-        <v>4.677822732913842</v>
+        <v>4.958267740882299</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.615882846677727</v>
+        <v>4.560931860407754</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1169364624946419</v>
+        <v>0.116746711382876</v>
       </c>
       <c r="C86">
-        <v>1.656086869711536</v>
+        <v>1.591645108762999</v>
       </c>
       <c r="D86">
-        <v>5.503286869711535</v>
+        <v>5.509645108762999</v>
       </c>
       <c r="E86">
-        <v>4.537199999999999</v>
+        <v>4.608</v>
       </c>
       <c r="F86">
-        <v>5.9472</v>
+        <v>6.018</v>
       </c>
       <c r="G86">
         <v>2.1</v>
@@ -8339,28 +8339,28 @@
         <v>1.5</v>
       </c>
       <c r="M86">
-        <v>0.32888016</v>
+        <v>0.3327954</v>
       </c>
       <c r="N86">
-        <v>1.17111984</v>
+        <v>1.1672046</v>
       </c>
       <c r="O86">
-        <v>0.234223968</v>
+        <v>0.23344092</v>
       </c>
       <c r="P86">
-        <v>0.936895872</v>
+        <v>0.93376368</v>
       </c>
       <c r="Q86">
-        <v>1.016895872</v>
+        <v>1.01376368</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.498592890591512</v>
+        <v>0.5276180758858396</v>
       </c>
       <c r="T86">
-        <v>4.958267740882296</v>
+        <v>5.276105416579879</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.560931860407755</v>
+        <v>4.507273838520605</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.116746711382876</v>
+        <v>0.11827696027111</v>
       </c>
       <c r="C87">
-        <v>1.591645108762999</v>
+        <v>1.469983706416923</v>
       </c>
       <c r="D87">
-        <v>5.509645108762999</v>
+        <v>5.458783706416923</v>
       </c>
       <c r="E87">
-        <v>4.608</v>
+        <v>4.6788</v>
       </c>
       <c r="F87">
-        <v>6.018</v>
+        <v>6.0888</v>
       </c>
       <c r="G87">
         <v>2.1</v>
@@ -8421,45 +8421,45 @@
         <v>1.5</v>
       </c>
       <c r="M87">
-        <v>0.3327954</v>
+        <v>0.35193264</v>
       </c>
       <c r="N87">
-        <v>1.1672046</v>
+        <v>1.14806736</v>
       </c>
       <c r="O87">
-        <v>0.23344092</v>
+        <v>0.229613472</v>
       </c>
       <c r="P87">
-        <v>0.93376368</v>
+        <v>0.9184538879999999</v>
       </c>
       <c r="Q87">
-        <v>1.01376368</v>
+        <v>0.998453888</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5276180758858396</v>
+        <v>0.5607897162222142</v>
       </c>
       <c r="T87">
-        <v>5.276105416579879</v>
+        <v>5.639348474519974</v>
       </c>
       <c r="U87">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V87">
         <v>0.2</v>
       </c>
       <c r="W87">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>4.507273838520605</v>
+        <v>4.262179262486139</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.11827696027111</v>
+        <v>0.118107209159344</v>
       </c>
       <c r="C88">
-        <v>1.469983706416923</v>
+        <v>1.404779428117538</v>
       </c>
       <c r="D88">
-        <v>5.458783706416923</v>
+        <v>5.464379428117538</v>
       </c>
       <c r="E88">
-        <v>4.6788</v>
+        <v>4.7496</v>
       </c>
       <c r="F88">
-        <v>6.0888</v>
+        <v>6.1596</v>
       </c>
       <c r="G88">
         <v>2.1</v>
@@ -8503,28 +8503,28 @@
         <v>1.5</v>
       </c>
       <c r="M88">
-        <v>0.35193264</v>
+        <v>0.35602488</v>
       </c>
       <c r="N88">
-        <v>1.14806736</v>
+        <v>1.14397512</v>
       </c>
       <c r="O88">
-        <v>0.229613472</v>
+        <v>0.228795024</v>
       </c>
       <c r="P88">
-        <v>0.9184538879999999</v>
+        <v>0.9151800959999999</v>
       </c>
       <c r="Q88">
-        <v>0.998453888</v>
+        <v>0.995180096</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5607897162222142</v>
+        <v>0.5990646858411078</v>
       </c>
       <c r="T88">
-        <v>5.639348474519974</v>
+        <v>6.058475079835469</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.262179262486139</v>
+        <v>4.213188696250666</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.118107209159344</v>
+        <v>0.1179374580475781</v>
       </c>
       <c r="C89">
-        <v>1.404779428117538</v>
+        <v>1.339586633779988</v>
       </c>
       <c r="D89">
-        <v>5.464379428117538</v>
+        <v>5.469986633779989</v>
       </c>
       <c r="E89">
-        <v>4.7496</v>
+        <v>4.8204</v>
       </c>
       <c r="F89">
-        <v>6.1596</v>
+        <v>6.2304</v>
       </c>
       <c r="G89">
         <v>2.1</v>
@@ -8585,28 +8585,28 @@
         <v>1.5</v>
       </c>
       <c r="M89">
-        <v>0.35602488</v>
+        <v>0.3601171200000001</v>
       </c>
       <c r="N89">
-        <v>1.14397512</v>
+        <v>1.13988288</v>
       </c>
       <c r="O89">
-        <v>0.228795024</v>
+        <v>0.227976576</v>
       </c>
       <c r="P89">
-        <v>0.9151800959999999</v>
+        <v>0.9119063040000001</v>
       </c>
       <c r="Q89">
-        <v>0.995180096</v>
+        <v>0.9919063040000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5990646858411078</v>
+        <v>0.6437188170631506</v>
       </c>
       <c r="T89">
-        <v>6.058475079835469</v>
+        <v>6.547456119370213</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.213188696250666</v>
+        <v>4.165311551975091</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1179374580475781</v>
+        <v>0.1177677069358121</v>
       </c>
       <c r="C90">
-        <v>1.339586633779988</v>
+        <v>1.274405358792969</v>
       </c>
       <c r="D90">
-        <v>5.469986633779989</v>
+        <v>5.47560535879297</v>
       </c>
       <c r="E90">
-        <v>4.8204</v>
+        <v>4.8912</v>
       </c>
       <c r="F90">
-        <v>6.2304</v>
+        <v>6.301200000000001</v>
       </c>
       <c r="G90">
         <v>2.1</v>
@@ -8667,28 +8667,28 @@
         <v>1.5</v>
       </c>
       <c r="M90">
-        <v>0.3601171200000001</v>
+        <v>0.36420936</v>
       </c>
       <c r="N90">
-        <v>1.13988288</v>
+        <v>1.13579064</v>
       </c>
       <c r="O90">
-        <v>0.227976576</v>
+        <v>0.227158128</v>
       </c>
       <c r="P90">
-        <v>0.9119063040000001</v>
+        <v>0.9086325119999999</v>
       </c>
       <c r="Q90">
-        <v>0.9919063040000001</v>
+        <v>0.988632512</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6437188170631506</v>
+        <v>0.6964918812346554</v>
       </c>
       <c r="T90">
-        <v>6.547456119370213</v>
+        <v>7.125342802456728</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.165311551975091</v>
+        <v>4.118510298582112</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1177677069358121</v>
+        <v>0.1175979558240461</v>
       </c>
       <c r="C91">
-        <v>1.274405358792969</v>
+        <v>1.209235638690723</v>
       </c>
       <c r="D91">
-        <v>5.47560535879297</v>
+        <v>5.481235638690722</v>
       </c>
       <c r="E91">
-        <v>4.8912</v>
+        <v>4.962</v>
       </c>
       <c r="F91">
-        <v>6.301200000000001</v>
+        <v>6.372</v>
       </c>
       <c r="G91">
         <v>2.1</v>
@@ -8749,28 +8749,28 @@
         <v>1.5</v>
       </c>
       <c r="M91">
-        <v>0.36420936</v>
+        <v>0.3683016</v>
       </c>
       <c r="N91">
-        <v>1.13579064</v>
+        <v>1.1316984</v>
       </c>
       <c r="O91">
-        <v>0.227158128</v>
+        <v>0.22633968</v>
       </c>
       <c r="P91">
-        <v>0.9086325119999999</v>
+        <v>0.90535872</v>
       </c>
       <c r="Q91">
-        <v>0.988632512</v>
+        <v>0.98535872</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6964918812346554</v>
+        <v>0.7598195582404615</v>
       </c>
       <c r="T91">
-        <v>7.125342802456728</v>
+        <v>7.818806822160547</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.118510298582112</v>
+        <v>4.072749073042311</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1175979558240461</v>
+        <v>0.1174282047122802</v>
       </c>
       <c r="C92">
-        <v>1.209235638690723</v>
+        <v>1.144077509153796</v>
       </c>
       <c r="D92">
-        <v>5.481235638690722</v>
+        <v>5.486877509153796</v>
       </c>
       <c r="E92">
-        <v>4.962</v>
+        <v>5.0328</v>
       </c>
       <c r="F92">
-        <v>6.372</v>
+        <v>6.4428</v>
       </c>
       <c r="G92">
         <v>2.1</v>
@@ -8831,28 +8831,28 @@
         <v>1.5</v>
       </c>
       <c r="M92">
-        <v>0.3683016</v>
+        <v>0.37239384</v>
       </c>
       <c r="N92">
-        <v>1.1316984</v>
+        <v>1.12760616</v>
       </c>
       <c r="O92">
-        <v>0.22633968</v>
+        <v>0.225521232</v>
       </c>
       <c r="P92">
-        <v>0.90535872</v>
+        <v>0.9020849280000001</v>
       </c>
       <c r="Q92">
-        <v>0.98535872</v>
+        <v>0.9820849280000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7598195582404615</v>
+        <v>0.8372200523586687</v>
       </c>
       <c r="T92">
-        <v>7.818806822160547</v>
+        <v>8.666373957354102</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.072749073042311</v>
+        <v>4.027993588723165</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1174282047122802</v>
+        <v>0.1198344536005142</v>
       </c>
       <c r="C93">
-        <v>1.144077509153796</v>
+        <v>0.9943720600930348</v>
       </c>
       <c r="D93">
-        <v>5.486877509153796</v>
+        <v>5.407972060093035</v>
       </c>
       <c r="E93">
-        <v>5.0328</v>
+        <v>5.1036</v>
       </c>
       <c r="F93">
-        <v>6.4428</v>
+        <v>6.5136</v>
       </c>
       <c r="G93">
         <v>2.1</v>
@@ -8913,45 +8913,45 @@
         <v>1.5</v>
       </c>
       <c r="M93">
-        <v>0.37239384</v>
+        <v>0.39928368</v>
       </c>
       <c r="N93">
-        <v>1.12760616</v>
+        <v>1.10071632</v>
       </c>
       <c r="O93">
-        <v>0.225521232</v>
+        <v>0.220143264</v>
       </c>
       <c r="P93">
-        <v>0.9020849280000001</v>
+        <v>0.880573056</v>
       </c>
       <c r="Q93">
-        <v>0.9820849280000001</v>
+        <v>0.9605730560000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8372200523586687</v>
+        <v>0.933970670006428</v>
       </c>
       <c r="T93">
-        <v>8.666373957354102</v>
+        <v>9.725832876346049</v>
       </c>
       <c r="U93">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V93">
         <v>0.2</v>
       </c>
       <c r="W93">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>4.027993588723165</v>
+        <v>3.756727547692408</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1198344536005142</v>
+        <v>0.1196927024887482</v>
       </c>
       <c r="C94">
-        <v>0.9943720600930348</v>
+        <v>0.9281573856123018</v>
       </c>
       <c r="D94">
-        <v>5.407972060093035</v>
+        <v>5.412557385612302</v>
       </c>
       <c r="E94">
-        <v>5.1036</v>
+        <v>5.1744</v>
       </c>
       <c r="F94">
-        <v>6.5136</v>
+        <v>6.5844</v>
       </c>
       <c r="G94">
         <v>2.1</v>
@@ -8995,28 +8995,28 @@
         <v>1.5</v>
       </c>
       <c r="M94">
-        <v>0.39928368</v>
+        <v>0.40362372</v>
       </c>
       <c r="N94">
-        <v>1.10071632</v>
+        <v>1.09637628</v>
       </c>
       <c r="O94">
-        <v>0.220143264</v>
+        <v>0.219275256</v>
       </c>
       <c r="P94">
-        <v>0.880573056</v>
+        <v>0.8771010239999999</v>
       </c>
       <c r="Q94">
-        <v>0.9605730560000001</v>
+        <v>0.957101024</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.933970670006428</v>
+        <v>1.058364321267833</v>
       </c>
       <c r="T94">
-        <v>9.725832876346049</v>
+        <v>11.08799434362141</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.756727547692408</v>
+        <v>3.716332627824747</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1196927024887482</v>
+        <v>0.1195509513769823</v>
       </c>
       <c r="C95">
-        <v>0.9281573856123018</v>
+        <v>0.861950493365617</v>
       </c>
       <c r="D95">
-        <v>5.412557385612302</v>
+        <v>5.417150493365618</v>
       </c>
       <c r="E95">
-        <v>5.1744</v>
+        <v>5.245200000000001</v>
       </c>
       <c r="F95">
-        <v>6.5844</v>
+        <v>6.655200000000001</v>
       </c>
       <c r="G95">
         <v>2.1</v>
@@ -9077,28 +9077,28 @@
         <v>1.5</v>
       </c>
       <c r="M95">
-        <v>0.40362372</v>
+        <v>0.4079637600000001</v>
       </c>
       <c r="N95">
-        <v>1.09637628</v>
+        <v>1.09203624</v>
       </c>
       <c r="O95">
-        <v>0.219275256</v>
+        <v>0.218407248</v>
       </c>
       <c r="P95">
-        <v>0.8771010239999999</v>
+        <v>0.8736289919999999</v>
       </c>
       <c r="Q95">
-        <v>0.957101024</v>
+        <v>0.953628992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.058364321267833</v>
+        <v>1.224222522949705</v>
       </c>
       <c r="T95">
-        <v>11.08799434362141</v>
+        <v>12.90420963332189</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.716332627824747</v>
+        <v>3.676797174337249</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1195509513769823</v>
+        <v>0.1194092002652163</v>
       </c>
       <c r="C96">
-        <v>0.861950493365617</v>
+        <v>0.7957514031818729</v>
       </c>
       <c r="D96">
-        <v>5.417150493365618</v>
+        <v>5.421751403181874</v>
       </c>
       <c r="E96">
-        <v>5.245200000000001</v>
+        <v>5.316000000000001</v>
       </c>
       <c r="F96">
-        <v>6.655200000000001</v>
+        <v>6.726000000000001</v>
       </c>
       <c r="G96">
         <v>2.1</v>
@@ -9159,28 +9159,28 @@
         <v>1.5</v>
       </c>
       <c r="M96">
-        <v>0.4079637600000001</v>
+        <v>0.4123038000000001</v>
       </c>
       <c r="N96">
-        <v>1.09203624</v>
+        <v>1.0876962</v>
       </c>
       <c r="O96">
-        <v>0.218407248</v>
+        <v>0.21753924</v>
       </c>
       <c r="P96">
-        <v>0.8736289919999999</v>
+        <v>0.8701569599999999</v>
       </c>
       <c r="Q96">
-        <v>0.953628992</v>
+        <v>0.9501569599999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.224222522949705</v>
+        <v>1.456424005304328</v>
       </c>
       <c r="T96">
-        <v>12.90420963332189</v>
+        <v>15.44691103890256</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.676797174337249</v>
+        <v>3.638094046186331</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1194092002652163</v>
+        <v>0.1192674491534503</v>
       </c>
       <c r="C97">
-        <v>0.7957514031818729</v>
+        <v>0.7295601349573788</v>
       </c>
       <c r="D97">
-        <v>5.421751403181874</v>
+        <v>5.426360134957378</v>
       </c>
       <c r="E97">
-        <v>5.316000000000001</v>
+        <v>5.3868</v>
       </c>
       <c r="F97">
-        <v>6.726000000000001</v>
+        <v>6.7968</v>
       </c>
       <c r="G97">
         <v>2.1</v>
@@ -9241,28 +9241,28 @@
         <v>1.5</v>
       </c>
       <c r="M97">
-        <v>0.4123038000000001</v>
+        <v>0.41664384</v>
       </c>
       <c r="N97">
-        <v>1.0876962</v>
+        <v>1.08335616</v>
       </c>
       <c r="O97">
-        <v>0.21753924</v>
+        <v>0.216671232</v>
       </c>
       <c r="P97">
-        <v>0.8701569599999999</v>
+        <v>0.8666849280000001</v>
       </c>
       <c r="Q97">
-        <v>0.9501569599999999</v>
+        <v>0.9466849280000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.456424005304328</v>
+        <v>1.804726228836262</v>
       </c>
       <c r="T97">
-        <v>15.44691103890256</v>
+        <v>19.26096314727357</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.638094046186331</v>
+        <v>3.600197233205224</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1192674491534504</v>
+        <v>0.1191256980416844</v>
       </c>
       <c r="C98">
-        <v>0.729560134957377</v>
+        <v>0.6633767086561519</v>
       </c>
       <c r="D98">
-        <v>5.426360134957378</v>
+        <v>5.430976708656151</v>
       </c>
       <c r="E98">
-        <v>5.3868</v>
+        <v>5.457599999999999</v>
       </c>
       <c r="F98">
-        <v>6.7968</v>
+        <v>6.867599999999999</v>
       </c>
       <c r="G98">
         <v>2.1</v>
@@ -9323,28 +9323,28 @@
         <v>1.5</v>
       </c>
       <c r="M98">
-        <v>0.41664384</v>
+        <v>0.42098388</v>
       </c>
       <c r="N98">
-        <v>1.08335616</v>
+        <v>1.07901612</v>
       </c>
       <c r="O98">
-        <v>0.216671232</v>
+        <v>0.215803224</v>
       </c>
       <c r="P98">
-        <v>0.8666849280000001</v>
+        <v>0.863212896</v>
       </c>
       <c r="Q98">
-        <v>0.9466849280000001</v>
+        <v>0.943212896</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.804726228836257</v>
+        <v>2.38522993472281</v>
       </c>
       <c r="T98">
-        <v>19.26096314727352</v>
+        <v>25.61771666122518</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.600197233205224</v>
+        <v>3.563081797811356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1191256980416844</v>
+        <v>0.1189839469299184</v>
       </c>
       <c r="C99">
-        <v>0.6633767086561519</v>
+        <v>0.5972011443102048</v>
       </c>
       <c r="D99">
-        <v>5.430976708656151</v>
+        <v>5.435601144310205</v>
       </c>
       <c r="E99">
-        <v>5.457599999999999</v>
+        <v>5.5284</v>
       </c>
       <c r="F99">
-        <v>6.867599999999999</v>
+        <v>6.9384</v>
       </c>
       <c r="G99">
         <v>2.1</v>
@@ -9405,28 +9405,28 @@
         <v>1.5</v>
       </c>
       <c r="M99">
-        <v>0.42098388</v>
+        <v>0.42532392</v>
       </c>
       <c r="N99">
-        <v>1.07901612</v>
+        <v>1.07467608</v>
       </c>
       <c r="O99">
-        <v>0.215803224</v>
+        <v>0.214935216</v>
       </c>
       <c r="P99">
-        <v>0.863212896</v>
+        <v>0.8597408640000002</v>
       </c>
       <c r="Q99">
-        <v>0.943212896</v>
+        <v>0.9397408640000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.38522993472281</v>
+        <v>3.546237346495917</v>
       </c>
       <c r="T99">
-        <v>25.61771666122518</v>
+        <v>38.33122368912849</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.563081797811356</v>
+        <v>3.526723820282669</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1189839469299184</v>
+        <v>0.1210597958181524</v>
       </c>
       <c r="C100">
-        <v>0.5972011443102048</v>
+        <v>0.4594565240811832</v>
       </c>
       <c r="D100">
-        <v>5.435601144310205</v>
+        <v>5.368656524081183</v>
       </c>
       <c r="E100">
-        <v>5.5284</v>
+        <v>5.5992</v>
       </c>
       <c r="F100">
-        <v>6.9384</v>
+        <v>7.0092</v>
       </c>
       <c r="G100">
         <v>2.1</v>
@@ -9487,129 +9487,47 @@
         <v>1.5</v>
       </c>
       <c r="M100">
-        <v>0.42532392</v>
+        <v>0.44928972</v>
       </c>
       <c r="N100">
-        <v>1.07467608</v>
+        <v>1.05071028</v>
       </c>
       <c r="O100">
-        <v>0.214935216</v>
+        <v>0.210142056</v>
       </c>
       <c r="P100">
-        <v>0.8597408640000002</v>
+        <v>0.8405682240000001</v>
       </c>
       <c r="Q100">
-        <v>0.9397408640000002</v>
+        <v>0.9205682240000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.546237346495917</v>
+        <v>7.029259581815237</v>
       </c>
       <c r="T100">
-        <v>38.33122368912849</v>
+        <v>76.47174477283843</v>
       </c>
       <c r="U100">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V100">
         <v>0.2</v>
       </c>
       <c r="W100">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y100">
-        <v>3.526723820282669</v>
+        <v>3.338602984283727</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1210597958181524</v>
-      </c>
-      <c r="C101">
-        <v>0.4594565240811832</v>
-      </c>
-      <c r="D101">
-        <v>5.368656524081183</v>
-      </c>
-      <c r="E101">
-        <v>5.5992</v>
-      </c>
-      <c r="F101">
-        <v>7.0092</v>
-      </c>
-      <c r="G101">
-        <v>2.1</v>
-      </c>
-      <c r="H101">
-        <v>5.67</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.58</v>
-      </c>
-      <c r="K101">
-        <v>0.08000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>1.5</v>
-      </c>
-      <c r="M101">
-        <v>0.44928972</v>
-      </c>
-      <c r="N101">
-        <v>1.05071028</v>
-      </c>
-      <c r="O101">
-        <v>0.210142056</v>
-      </c>
-      <c r="P101">
-        <v>0.8405682240000001</v>
-      </c>
-      <c r="Q101">
-        <v>0.9205682240000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.029259581815237</v>
-      </c>
-      <c r="T101">
-        <v>76.47174477283843</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05128000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.338602984283727</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
